--- a/AutosurveillanceTemplates/THERMO.xlsx
+++ b/AutosurveillanceTemplates/THERMO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80875CFF-90A4-4763-B69F-BB2A626BE347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C2AE19-E46F-4158-B6DB-431425A84629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thermo" sheetId="62" r:id="rId1"/>
@@ -30,12 +30,13 @@
     <definedName name="LISTE_1">PARAM!$A$21:$A$23</definedName>
     <definedName name="LISTE_2">PARAM!$B$21:$B$24</definedName>
     <definedName name="LISTE_3">PARAM!$C$21:$C$25</definedName>
-    <definedName name="LISTE_4">PARAM!$D$21:$D$27</definedName>
+    <definedName name="LISTE_4">PARAM!$D$21:$D$25</definedName>
     <definedName name="LISTE_5">PARAM!$F$21:$F$25</definedName>
     <definedName name="LISTE_6">PARAM!$G$21</definedName>
-    <definedName name="Montage_sonde">PARAM!$G$44:$G$46</definedName>
-    <definedName name="Q_en_charge">PARAM!$A$30:$A$36</definedName>
-    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$39</definedName>
+    <definedName name="LISTE_7">PARAM!$H$21:$H$23</definedName>
+    <definedName name="Montage_sonde">PARAM!$G$44:$G$47</definedName>
+    <definedName name="Q_en_charge">PARAM!$A$30:$A$34</definedName>
+    <definedName name="Q_Gravitaire">PARAM!$B$30:$B$38</definedName>
     <definedName name="Satisfaction">PARAM!$D$44:$D$46</definedName>
     <definedName name="Type_capteur">PARAM!$C$44:$C$48</definedName>
     <definedName name="Type_equipement">PARAM!$C$4:$C$6</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="318">
   <si>
     <t>Pluviomètre</t>
   </si>
@@ -1131,9 +1132,6 @@
     <t>En W</t>
   </si>
   <si>
-    <t>En direct</t>
-  </si>
-  <si>
     <t>Thermomètre</t>
   </si>
   <si>
@@ -1758,6 +1756,39 @@
   </si>
   <si>
     <t>La vanne de prélèvement est-elle asservie au débit, ou au volume écoulé, et assure-t-elle un nombre de prélèvements égal, en moyenne, à au moins à 6 par heure de rejet effectif ? soit 144 prélèvements unitaires par 24h de rejet.</t>
+  </si>
+  <si>
+    <t>LISTE_7</t>
+  </si>
+  <si>
+    <t>Entre 10 et 20%</t>
+  </si>
+  <si>
+    <t>Non validé (&gt;20%)</t>
+  </si>
+  <si>
+    <t>Type réseau</t>
+  </si>
+  <si>
+    <t>Q en charge boues</t>
+  </si>
+  <si>
+    <t>Mixte</t>
+  </si>
+  <si>
+    <t>Débitmètre électromagnétique (boue/MDV)</t>
+  </si>
+  <si>
+    <t>Unitaire</t>
+  </si>
+  <si>
+    <t>Séparatif</t>
+  </si>
+  <si>
+    <t>En /</t>
+  </si>
+  <si>
+    <t>En N</t>
   </si>
 </sst>
 </file>
@@ -2196,7 +2227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="90">
+  <borders count="89">
     <border>
       <left/>
       <right/>
@@ -3268,19 +3299,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -3330,7 +3348,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3752,9 +3770,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3776,15 +3791,15 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="83" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="87" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="88" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="89" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3830,9 +3845,6 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="85" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3842,11 +3854,188 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="56" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="57" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -3869,6 +4058,33 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3881,219 +4097,18 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="56" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="57" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="9" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="9" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4512,9 +4527,9 @@
     <col min="1" max="2" width="2.703125" style="78" customWidth="1"/>
     <col min="3" max="18" width="10.703125" style="78"/>
     <col min="19" max="19" width="2.703125" style="78" customWidth="1"/>
-    <col min="20" max="20" width="2.703125" style="247" customWidth="1"/>
-    <col min="21" max="21" width="10.703125" style="248"/>
-    <col min="22" max="26" width="10.703125" style="247"/>
+    <col min="20" max="20" width="2.703125" style="175" customWidth="1"/>
+    <col min="21" max="21" width="10.703125" style="176"/>
+    <col min="22" max="26" width="10.703125" style="175"/>
     <col min="27" max="16384" width="10.703125" style="78"/>
   </cols>
   <sheetData>
@@ -4540,131 +4555,131 @@
     </row>
     <row r="2" spans="2:19" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="66"/>
-      <c r="C2" s="209" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="210"/>
-      <c r="P2" s="210"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="211"/>
+      <c r="C2" s="217" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="218"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="219"/>
       <c r="S2" s="67"/>
     </row>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="68"/>
-      <c r="C3" s="212" t="s">
-        <v>215</v>
-      </c>
-      <c r="D3" s="204"/>
-      <c r="E3" s="203"/>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="204" t="s">
-        <v>211</v>
-      </c>
-      <c r="I3" s="204"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="204" t="s">
-        <v>213</v>
-      </c>
-      <c r="N3" s="204"/>
-      <c r="O3" s="204"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="208"/>
+      <c r="C3" s="220" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="221"/>
+      <c r="E3" s="222"/>
+      <c r="F3" s="222"/>
+      <c r="G3" s="222"/>
+      <c r="H3" s="221" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="221"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="221" t="s">
+        <v>212</v>
+      </c>
+      <c r="N3" s="221"/>
+      <c r="O3" s="221"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="216"/>
       <c r="S3" s="69"/>
     </row>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="68"/>
-      <c r="C4" s="212" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="204"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="204" t="s">
-        <v>216</v>
-      </c>
-      <c r="I4" s="204"/>
-      <c r="J4" s="203"/>
-      <c r="K4" s="203"/>
-      <c r="L4" s="203"/>
-      <c r="M4" s="204" t="s">
-        <v>218</v>
-      </c>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="208"/>
+      <c r="C4" s="220" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" s="221"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="221" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="221"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
+      <c r="M4" s="221" t="s">
+        <v>217</v>
+      </c>
+      <c r="N4" s="221"/>
+      <c r="O4" s="221"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="216"/>
       <c r="S4" s="69"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="68"/>
-      <c r="C5" s="212" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="204"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="204" t="s">
-        <v>217</v>
-      </c>
-      <c r="I5" s="204"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="204" t="s">
-        <v>214</v>
-      </c>
-      <c r="N5" s="204"/>
-      <c r="O5" s="204"/>
-      <c r="P5" s="205"/>
-      <c r="Q5" s="205"/>
-      <c r="R5" s="206"/>
+      <c r="C5" s="220" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="221"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="221" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="221"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="221" t="s">
+        <v>213</v>
+      </c>
+      <c r="N5" s="221"/>
+      <c r="O5" s="221"/>
+      <c r="P5" s="225"/>
+      <c r="Q5" s="225"/>
+      <c r="R5" s="226"/>
       <c r="S5" s="69"/>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="68"/>
-      <c r="C6" s="200" t="s">
-        <v>210</v>
-      </c>
-      <c r="D6" s="201"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="201" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" s="201"/>
-      <c r="J6" s="202" t="str">
+      <c r="C6" s="227" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="228"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="228" t="s">
+        <v>211</v>
+      </c>
+      <c r="I6" s="228"/>
+      <c r="J6" s="229" t="str">
         <f>D26</f>
         <v>Thermomètre</v>
       </c>
-      <c r="K6" s="202"/>
-      <c r="L6" s="202"/>
-      <c r="M6" s="201" t="s">
-        <v>219</v>
-      </c>
-      <c r="N6" s="201"/>
-      <c r="O6" s="201"/>
-      <c r="P6" s="213"/>
-      <c r="Q6" s="213"/>
-      <c r="R6" s="214"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="229"/>
+      <c r="M6" s="228" t="s">
+        <v>218</v>
+      </c>
+      <c r="N6" s="228"/>
+      <c r="O6" s="228"/>
+      <c r="P6" s="223"/>
+      <c r="Q6" s="223"/>
+      <c r="R6" s="224"/>
       <c r="S6" s="69"/>
     </row>
     <row r="7" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -4689,24 +4704,24 @@
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="70"/>
-      <c r="C8" s="191" t="s">
-        <v>205</v>
-      </c>
-      <c r="D8" s="192"/>
-      <c r="E8" s="192"/>
-      <c r="F8" s="192"/>
-      <c r="G8" s="192"/>
-      <c r="H8" s="192"/>
-      <c r="I8" s="192"/>
-      <c r="J8" s="192"/>
-      <c r="K8" s="192"/>
-      <c r="L8" s="192"/>
-      <c r="M8" s="192"/>
-      <c r="N8" s="192"/>
-      <c r="O8" s="192"/>
-      <c r="P8" s="192"/>
-      <c r="Q8" s="192"/>
-      <c r="R8" s="193"/>
+      <c r="C8" s="189" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="190"/>
+      <c r="E8" s="190"/>
+      <c r="F8" s="190"/>
+      <c r="G8" s="190"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="190"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="190"/>
+      <c r="L8" s="190"/>
+      <c r="M8" s="190"/>
+      <c r="N8" s="190"/>
+      <c r="O8" s="190"/>
+      <c r="P8" s="190"/>
+      <c r="Q8" s="190"/>
+      <c r="R8" s="191"/>
       <c r="S8" s="71"/>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -4732,94 +4747,94 @@
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="79"/>
       <c r="C10" s="84"/>
-      <c r="D10" s="194" t="s">
-        <v>194</v>
-      </c>
-      <c r="E10" s="195"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="195"/>
-      <c r="I10" s="195"/>
-      <c r="J10" s="195"/>
-      <c r="K10" s="195"/>
-      <c r="L10" s="195"/>
-      <c r="M10" s="195"/>
-      <c r="N10" s="195"/>
-      <c r="O10" s="195"/>
-      <c r="P10" s="195"/>
-      <c r="Q10" s="196"/>
+      <c r="D10" s="212" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="213"/>
+      <c r="F10" s="213"/>
+      <c r="G10" s="213"/>
+      <c r="H10" s="213"/>
+      <c r="I10" s="213"/>
+      <c r="J10" s="213"/>
+      <c r="K10" s="213"/>
+      <c r="L10" s="213"/>
+      <c r="M10" s="213"/>
+      <c r="N10" s="213"/>
+      <c r="O10" s="213"/>
+      <c r="P10" s="213"/>
+      <c r="Q10" s="214"/>
       <c r="R10" s="85"/>
       <c r="S10" s="80"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="79"/>
       <c r="C11" s="84"/>
-      <c r="D11" s="179" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="180"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="182"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
-      <c r="K11" s="179" t="s">
-        <v>223</v>
-      </c>
-      <c r="L11" s="180"/>
-      <c r="M11" s="181"/>
-      <c r="N11" s="197"/>
-      <c r="O11" s="198"/>
-      <c r="P11" s="198"/>
-      <c r="Q11" s="199"/>
+      <c r="D11" s="230" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="231"/>
+      <c r="F11" s="232"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="234"/>
+      <c r="I11" s="234"/>
+      <c r="J11" s="235"/>
+      <c r="K11" s="230" t="s">
+        <v>222</v>
+      </c>
+      <c r="L11" s="231"/>
+      <c r="M11" s="232"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="237"/>
+      <c r="P11" s="237"/>
+      <c r="Q11" s="238"/>
       <c r="R11" s="85"/>
       <c r="S11" s="80"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="79"/>
       <c r="C12" s="84"/>
-      <c r="D12" s="179" t="s">
-        <v>221</v>
-      </c>
-      <c r="E12" s="180"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="182"/>
-      <c r="H12" s="183"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="179" t="s">
-        <v>224</v>
-      </c>
-      <c r="L12" s="180"/>
-      <c r="M12" s="181"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="183"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="184"/>
+      <c r="D12" s="230" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="231"/>
+      <c r="F12" s="232"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="234"/>
+      <c r="I12" s="234"/>
+      <c r="J12" s="235"/>
+      <c r="K12" s="230" t="s">
+        <v>223</v>
+      </c>
+      <c r="L12" s="231"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="233"/>
+      <c r="O12" s="234"/>
+      <c r="P12" s="234"/>
+      <c r="Q12" s="235"/>
       <c r="R12" s="85"/>
       <c r="S12" s="80"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="79"/>
       <c r="C13" s="84"/>
-      <c r="D13" s="179" t="s">
-        <v>222</v>
-      </c>
-      <c r="E13" s="180"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="182"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="184"/>
-      <c r="K13" s="179" t="s">
-        <v>225</v>
-      </c>
-      <c r="L13" s="180"/>
-      <c r="M13" s="181"/>
-      <c r="N13" s="188"/>
-      <c r="O13" s="189"/>
-      <c r="P13" s="189"/>
-      <c r="Q13" s="190"/>
+      <c r="D13" s="230" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="231"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="233"/>
+      <c r="H13" s="234"/>
+      <c r="I13" s="234"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="230" t="s">
+        <v>224</v>
+      </c>
+      <c r="L13" s="231"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="240"/>
+      <c r="P13" s="240"/>
+      <c r="Q13" s="241"/>
       <c r="R13" s="85"/>
       <c r="S13" s="80"/>
     </row>
@@ -4846,70 +4861,70 @@
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="79"/>
       <c r="C15" s="84"/>
-      <c r="D15" s="178" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="178"/>
-      <c r="F15" s="178"/>
-      <c r="G15" s="178"/>
-      <c r="H15" s="178"/>
-      <c r="I15" s="178"/>
-      <c r="J15" s="178"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="178"/>
-      <c r="M15" s="178"/>
-      <c r="N15" s="178"/>
-      <c r="O15" s="178"/>
-      <c r="P15" s="178"/>
-      <c r="Q15" s="178"/>
+      <c r="D15" s="242" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" s="242"/>
+      <c r="F15" s="242"/>
+      <c r="G15" s="242"/>
+      <c r="H15" s="242"/>
+      <c r="I15" s="242"/>
+      <c r="J15" s="242"/>
+      <c r="K15" s="242"/>
+      <c r="L15" s="242"/>
+      <c r="M15" s="242"/>
+      <c r="N15" s="242"/>
+      <c r="O15" s="242"/>
+      <c r="P15" s="242"/>
+      <c r="Q15" s="242"/>
       <c r="R15" s="85"/>
       <c r="S15" s="80"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B16" s="79"/>
       <c r="C16" s="84"/>
-      <c r="D16" s="179" t="s">
-        <v>220</v>
-      </c>
-      <c r="E16" s="180"/>
-      <c r="F16" s="181"/>
-      <c r="G16" s="182"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="179" t="s">
-        <v>226</v>
-      </c>
-      <c r="L16" s="180"/>
-      <c r="M16" s="181"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="183"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
+      <c r="D16" s="230" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="231"/>
+      <c r="F16" s="232"/>
+      <c r="G16" s="233"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="234"/>
+      <c r="J16" s="235"/>
+      <c r="K16" s="230" t="s">
+        <v>225</v>
+      </c>
+      <c r="L16" s="231"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="233"/>
+      <c r="O16" s="234"/>
+      <c r="P16" s="234"/>
+      <c r="Q16" s="235"/>
       <c r="R16" s="85"/>
       <c r="S16" s="80"/>
     </row>
     <row r="17" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B17" s="79"/>
       <c r="C17" s="84"/>
-      <c r="D17" s="179" t="s">
-        <v>221</v>
-      </c>
-      <c r="E17" s="180"/>
-      <c r="F17" s="181"/>
-      <c r="G17" s="182"/>
-      <c r="H17" s="183"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="184"/>
-      <c r="K17" s="179" t="s">
-        <v>227</v>
-      </c>
-      <c r="L17" s="180"/>
-      <c r="M17" s="181"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="186"/>
-      <c r="P17" s="186"/>
-      <c r="Q17" s="187"/>
+      <c r="D17" s="230" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="231"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="233"/>
+      <c r="H17" s="234"/>
+      <c r="I17" s="234"/>
+      <c r="J17" s="235"/>
+      <c r="K17" s="230" t="s">
+        <v>226</v>
+      </c>
+      <c r="L17" s="231"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="243"/>
+      <c r="O17" s="244"/>
+      <c r="P17" s="244"/>
+      <c r="Q17" s="245"/>
       <c r="R17" s="85"/>
       <c r="S17" s="80"/>
     </row>
@@ -4936,18 +4951,18 @@
     <row r="19" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="79"/>
       <c r="C19" s="84"/>
-      <c r="D19" s="194" t="s">
-        <v>191</v>
-      </c>
-      <c r="E19" s="195"/>
-      <c r="F19" s="195"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="195"/>
-      <c r="I19" s="195"/>
-      <c r="J19" s="195"/>
-      <c r="K19" s="195"/>
-      <c r="L19" s="195"/>
-      <c r="M19" s="196"/>
+      <c r="D19" s="212" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="213"/>
+      <c r="F19" s="213"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="213"/>
+      <c r="J19" s="213"/>
+      <c r="K19" s="213"/>
+      <c r="L19" s="213"/>
+      <c r="M19" s="214"/>
       <c r="N19" s="77"/>
       <c r="O19" s="77"/>
       <c r="P19" s="77"/>
@@ -4958,56 +4973,56 @@
     <row r="20" spans="2:26" s="76" customFormat="1" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="73"/>
       <c r="C20" s="86"/>
-      <c r="D20" s="215" t="s">
+      <c r="D20" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="215"/>
-      <c r="F20" s="216" t="s">
-        <v>204</v>
-      </c>
-      <c r="G20" s="215"/>
-      <c r="H20" s="216" t="s">
+      <c r="E20" s="209"/>
+      <c r="F20" s="210" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="209"/>
+      <c r="H20" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I20" s="216"/>
-      <c r="J20" s="216" t="s">
+      <c r="I20" s="210"/>
+      <c r="J20" s="210" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="216"/>
-      <c r="L20" s="217" t="s">
-        <v>192</v>
-      </c>
-      <c r="M20" s="217"/>
+      <c r="K20" s="210"/>
+      <c r="L20" s="211" t="s">
+        <v>191</v>
+      </c>
+      <c r="M20" s="211"/>
       <c r="N20" s="74"/>
       <c r="O20" s="74"/>
       <c r="P20" s="74"/>
       <c r="Q20" s="74"/>
       <c r="R20" s="87"/>
       <c r="S20" s="75"/>
-      <c r="T20" s="249"/>
-      <c r="U20" s="250"/>
-      <c r="V20" s="249"/>
-      <c r="W20" s="249"/>
-      <c r="X20" s="249"/>
-      <c r="Y20" s="249"/>
-      <c r="Z20" s="249"/>
+      <c r="T20" s="177"/>
+      <c r="U20" s="178"/>
+      <c r="V20" s="177"/>
+      <c r="W20" s="177"/>
+      <c r="X20" s="177"/>
+      <c r="Y20" s="177"/>
+      <c r="Z20" s="177"/>
     </row>
     <row r="21" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="79"/>
       <c r="C21" s="84"/>
-      <c r="D21" s="225"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="225"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="225"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="225"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="227" t="str">
+      <c r="D21" s="199"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="199"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="199"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="199"/>
+      <c r="K21" s="200"/>
+      <c r="L21" s="201" t="str">
         <f>IF(H21&gt;0,H21-J21,"-")</f>
         <v>-</v>
       </c>
-      <c r="M21" s="228"/>
+      <c r="M21" s="202"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -5057,24 +5072,24 @@
     </row>
     <row r="24" spans="2:26" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="79"/>
-      <c r="C24" s="191" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="192"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="192"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="192"/>
-      <c r="I24" s="192"/>
-      <c r="J24" s="192"/>
-      <c r="K24" s="192"/>
-      <c r="L24" s="192"/>
-      <c r="M24" s="192"/>
-      <c r="N24" s="192"/>
-      <c r="O24" s="192"/>
-      <c r="P24" s="192"/>
-      <c r="Q24" s="192"/>
-      <c r="R24" s="193"/>
+      <c r="C24" s="189" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="190"/>
+      <c r="E24" s="190"/>
+      <c r="F24" s="190"/>
+      <c r="G24" s="190"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="190"/>
+      <c r="J24" s="190"/>
+      <c r="K24" s="190"/>
+      <c r="L24" s="190"/>
+      <c r="M24" s="190"/>
+      <c r="N24" s="190"/>
+      <c r="O24" s="190"/>
+      <c r="P24" s="190"/>
+      <c r="Q24" s="190"/>
+      <c r="R24" s="191"/>
       <c r="S24" s="80"/>
     </row>
     <row r="25" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5100,55 +5115,55 @@
     <row r="26" spans="2:26" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="79"/>
       <c r="C26" s="91"/>
-      <c r="D26" s="229" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="229"/>
-      <c r="F26" s="229"/>
-      <c r="G26" s="229"/>
-      <c r="H26" s="229"/>
-      <c r="I26" s="229"/>
-      <c r="J26" s="229"/>
-      <c r="K26" s="229"/>
-      <c r="L26" s="229"/>
-      <c r="M26" s="229"/>
-      <c r="N26" s="229"/>
-      <c r="O26" s="229"/>
-      <c r="P26" s="229"/>
-      <c r="Q26" s="229"/>
+      <c r="D26" s="203" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="203"/>
+      <c r="F26" s="203"/>
+      <c r="G26" s="203"/>
+      <c r="H26" s="203"/>
+      <c r="I26" s="203"/>
+      <c r="J26" s="203"/>
+      <c r="K26" s="203"/>
+      <c r="L26" s="203"/>
+      <c r="M26" s="203"/>
+      <c r="N26" s="203"/>
+      <c r="O26" s="203"/>
+      <c r="P26" s="203"/>
+      <c r="Q26" s="203"/>
       <c r="R26" s="92"/>
       <c r="S26" s="80"/>
     </row>
     <row r="27" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B27" s="79"/>
       <c r="C27" s="91"/>
-      <c r="D27" s="237" t="s">
+      <c r="D27" s="179" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="180"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="180"/>
+      <c r="H27" s="180"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="179" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="180"/>
+      <c r="L27" s="180"/>
+      <c r="M27" s="181"/>
+      <c r="N27" s="204" t="s">
+        <v>77</v>
+      </c>
+      <c r="O27" s="204"/>
+      <c r="P27" s="98" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="238"/>
-      <c r="F27" s="238"/>
-      <c r="G27" s="238"/>
-      <c r="H27" s="238"/>
-      <c r="I27" s="239"/>
-      <c r="J27" s="237" t="s">
-        <v>176</v>
-      </c>
-      <c r="K27" s="238"/>
-      <c r="L27" s="238"/>
-      <c r="M27" s="239"/>
-      <c r="N27" s="230" t="s">
-        <v>77</v>
-      </c>
-      <c r="O27" s="230"/>
-      <c r="P27" s="98" t="s">
-        <v>190</v>
-      </c>
       <c r="Q27" s="98" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R27" s="92"/>
       <c r="S27" s="80"/>
-      <c r="U27" s="248" t="s">
+      <c r="U27" s="176" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5158,23 +5173,23 @@
       <c r="D28" s="93">
         <v>1</v>
       </c>
-      <c r="E28" s="240" t="str">
+      <c r="E28" s="182" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D28+2,FALSE),"-")</f>
         <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
       </c>
-      <c r="F28" s="241"/>
-      <c r="G28" s="241"/>
-      <c r="H28" s="241"/>
-      <c r="I28" s="241"/>
-      <c r="J28" s="240" t="str">
+      <c r="F28" s="183"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="182" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D28+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
       </c>
-      <c r="K28" s="241"/>
-      <c r="L28" s="241"/>
-      <c r="M28" s="244"/>
-      <c r="N28" s="235"/>
-      <c r="O28" s="236"/>
+      <c r="K28" s="183"/>
+      <c r="L28" s="183"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="187"/>
+      <c r="O28" s="188"/>
       <c r="P28" s="99">
         <f>IF(OR(N28="Validé",N28="Réserve",N28="Oui"),Q28,0)</f>
         <v>0</v>
@@ -5185,7 +5200,7 @@
       </c>
       <c r="R28" s="92"/>
       <c r="S28" s="80"/>
-      <c r="U28" s="248" t="s">
+      <c r="U28" s="176" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5195,23 +5210,23 @@
       <c r="D29" s="93">
         <v>2</v>
       </c>
-      <c r="E29" s="240" t="str">
+      <c r="E29" s="182" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D29+2,FALSE),"-")</f>
         <v>La sonde est-elle installée conformément aux règles de l'art et/ou aux prescriptions des constructeurs ?</v>
       </c>
-      <c r="F29" s="241"/>
-      <c r="G29" s="241"/>
-      <c r="H29" s="241"/>
-      <c r="I29" s="241"/>
-      <c r="J29" s="240" t="str">
+      <c r="F29" s="183"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="182" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D29+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>Dans le canal de rejet, au centre de l'écoulement, à 2/3 de la profondeur et façon à être toujours immergé et à l'ombre.</v>
       </c>
-      <c r="K29" s="241"/>
-      <c r="L29" s="241"/>
-      <c r="M29" s="244"/>
-      <c r="N29" s="235"/>
-      <c r="O29" s="236"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="183"/>
+      <c r="M29" s="184"/>
+      <c r="N29" s="187"/>
+      <c r="O29" s="188"/>
       <c r="P29" s="99">
         <f t="shared" ref="P29:P31" si="0">IF(OR(N29="Validé",N29="Réserve",N29="Oui"),Q29,0)</f>
         <v>0</v>
@@ -5222,7 +5237,7 @@
       </c>
       <c r="R29" s="92"/>
       <c r="S29" s="80"/>
-      <c r="U29" s="248" t="s">
+      <c r="U29" s="176" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5232,24 +5247,24 @@
       <c r="D30" s="93">
         <v>3</v>
       </c>
-      <c r="E30" s="240" t="str">
+      <c r="E30" s="182" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D30+2,FALSE),"-")</f>
         <v>La propreté et l'état d'entretien de la sonde, sont-ils satisfaisants ?</v>
       </c>
-      <c r="F30" s="241"/>
-      <c r="G30" s="241"/>
-      <c r="H30" s="241"/>
-      <c r="I30" s="241"/>
-      <c r="J30" s="240" t="str">
+      <c r="F30" s="183"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="183"/>
+      <c r="J30" s="182" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D30+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
 Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
       </c>
-      <c r="K30" s="241"/>
-      <c r="L30" s="241"/>
-      <c r="M30" s="244"/>
-      <c r="N30" s="235"/>
-      <c r="O30" s="236"/>
+      <c r="K30" s="183"/>
+      <c r="L30" s="183"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="187"/>
+      <c r="O30" s="188"/>
       <c r="P30" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5260,7 +5275,7 @@
       </c>
       <c r="R30" s="92"/>
       <c r="S30" s="80"/>
-      <c r="U30" s="248" t="s">
+      <c r="U30" s="176" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5270,26 +5285,26 @@
       <c r="D31" s="93">
         <v>4</v>
       </c>
-      <c r="E31" s="240" t="str">
+      <c r="E31" s="182" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D31+2,FALSE),"-")</f>
         <v>L'écart entre d'une part la mesure de la température réalisée à partir du dispositif en place et celle réalisée par l'organisme de contrôle d'autre part, est-il cohérent (EMT ± 1°C) ?</v>
       </c>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="240" t="str">
+      <c r="F31" s="183"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="183"/>
+      <c r="I31" s="183"/>
+      <c r="J31" s="182" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D31+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>-</v>
       </c>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
-      <c r="M31" s="244"/>
-      <c r="N31" s="235" t="str">
+      <c r="K31" s="183"/>
+      <c r="L31" s="183"/>
+      <c r="M31" s="184"/>
+      <c r="N31" s="187" t="str">
         <f>IF(L21&lt;&gt;"-",IF(ABS(L21)&lt;=1,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O31" s="236"/>
+      <c r="O31" s="188"/>
       <c r="P31" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5300,57 +5315,57 @@
       </c>
       <c r="R31" s="92"/>
       <c r="S31" s="80"/>
-      <c r="U31" s="248" t="s">
+      <c r="U31" s="176" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="79"/>
       <c r="C32" s="91"/>
-      <c r="D32" s="242" t="s">
+      <c r="D32" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="242"/>
-      <c r="F32" s="242"/>
-      <c r="G32" s="242"/>
-      <c r="H32" s="242"/>
-      <c r="I32" s="242"/>
-      <c r="J32" s="242"/>
-      <c r="K32" s="242"/>
-      <c r="L32" s="242"/>
-      <c r="M32" s="242"/>
-      <c r="N32" s="243"/>
-      <c r="O32" s="243"/>
-      <c r="P32" s="243" t="s">
+      <c r="E32" s="185"/>
+      <c r="F32" s="185"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
+      <c r="N32" s="186"/>
+      <c r="O32" s="186"/>
+      <c r="P32" s="186" t="s">
         <v>6</v>
       </c>
-      <c r="Q32" s="243"/>
+      <c r="Q32" s="186"/>
       <c r="R32" s="92"/>
       <c r="S32" s="80"/>
     </row>
     <row r="33" spans="2:19" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="79"/>
       <c r="C33" s="91"/>
-      <c r="D33" s="231"/>
-      <c r="E33" s="231"/>
-      <c r="F33" s="231"/>
-      <c r="G33" s="231"/>
-      <c r="H33" s="231"/>
-      <c r="I33" s="231"/>
-      <c r="J33" s="231"/>
-      <c r="K33" s="231"/>
-      <c r="L33" s="231"/>
-      <c r="M33" s="231"/>
-      <c r="N33" s="232" t="str">
+      <c r="D33" s="205"/>
+      <c r="E33" s="205"/>
+      <c r="F33" s="205"/>
+      <c r="G33" s="205"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="205"/>
+      <c r="M33" s="205"/>
+      <c r="N33" s="206" t="str">
         <f>IF(P33&gt;80,"Validé",IF(P33&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O33" s="232"/>
-      <c r="P33" s="233">
+      <c r="O33" s="206"/>
+      <c r="P33" s="207">
         <f>IF(SUM(P28:P31)&gt;100,100,SUM(P28:P31))</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="234"/>
+      <c r="Q33" s="208"/>
       <c r="R33" s="92"/>
       <c r="S33" s="80"/>
     </row>
@@ -5396,124 +5411,124 @@
     </row>
     <row r="36" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="79"/>
-      <c r="C36" s="191" t="s">
-        <v>207</v>
-      </c>
-      <c r="D36" s="192"/>
-      <c r="E36" s="192"/>
-      <c r="F36" s="192"/>
-      <c r="G36" s="192"/>
-      <c r="H36" s="192"/>
-      <c r="I36" s="192"/>
-      <c r="J36" s="192"/>
-      <c r="K36" s="192"/>
-      <c r="L36" s="192"/>
-      <c r="M36" s="192"/>
-      <c r="N36" s="192"/>
-      <c r="O36" s="192"/>
-      <c r="P36" s="192"/>
-      <c r="Q36" s="192"/>
-      <c r="R36" s="193"/>
+      <c r="C36" s="189" t="s">
+        <v>206</v>
+      </c>
+      <c r="D36" s="190"/>
+      <c r="E36" s="190"/>
+      <c r="F36" s="190"/>
+      <c r="G36" s="190"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="190"/>
+      <c r="J36" s="190"/>
+      <c r="K36" s="190"/>
+      <c r="L36" s="190"/>
+      <c r="M36" s="190"/>
+      <c r="N36" s="190"/>
+      <c r="O36" s="190"/>
+      <c r="P36" s="190"/>
+      <c r="Q36" s="190"/>
+      <c r="R36" s="191"/>
       <c r="S36" s="80"/>
     </row>
     <row r="37" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B37" s="79"/>
-      <c r="C37" s="218"/>
-      <c r="D37" s="219"/>
-      <c r="E37" s="219"/>
-      <c r="F37" s="219"/>
-      <c r="G37" s="219"/>
-      <c r="H37" s="219"/>
-      <c r="I37" s="219"/>
-      <c r="J37" s="219"/>
-      <c r="K37" s="219"/>
-      <c r="L37" s="219"/>
-      <c r="M37" s="219"/>
-      <c r="N37" s="219"/>
-      <c r="O37" s="219"/>
-      <c r="P37" s="219"/>
-      <c r="Q37" s="219"/>
-      <c r="R37" s="220"/>
+      <c r="C37" s="192"/>
+      <c r="D37" s="193"/>
+      <c r="E37" s="193"/>
+      <c r="F37" s="193"/>
+      <c r="G37" s="193"/>
+      <c r="H37" s="193"/>
+      <c r="I37" s="193"/>
+      <c r="J37" s="193"/>
+      <c r="K37" s="193"/>
+      <c r="L37" s="193"/>
+      <c r="M37" s="193"/>
+      <c r="N37" s="193"/>
+      <c r="O37" s="193"/>
+      <c r="P37" s="193"/>
+      <c r="Q37" s="193"/>
+      <c r="R37" s="194"/>
       <c r="S37" s="80"/>
     </row>
     <row r="38" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="79"/>
-      <c r="C38" s="221"/>
-      <c r="D38" s="219"/>
-      <c r="E38" s="219"/>
-      <c r="F38" s="219"/>
-      <c r="G38" s="219"/>
-      <c r="H38" s="219"/>
-      <c r="I38" s="219"/>
-      <c r="J38" s="219"/>
-      <c r="K38" s="219"/>
-      <c r="L38" s="219"/>
-      <c r="M38" s="219"/>
-      <c r="N38" s="219"/>
-      <c r="O38" s="219"/>
-      <c r="P38" s="219"/>
-      <c r="Q38" s="219"/>
-      <c r="R38" s="220"/>
+      <c r="C38" s="195"/>
+      <c r="D38" s="193"/>
+      <c r="E38" s="193"/>
+      <c r="F38" s="193"/>
+      <c r="G38" s="193"/>
+      <c r="H38" s="193"/>
+      <c r="I38" s="193"/>
+      <c r="J38" s="193"/>
+      <c r="K38" s="193"/>
+      <c r="L38" s="193"/>
+      <c r="M38" s="193"/>
+      <c r="N38" s="193"/>
+      <c r="O38" s="193"/>
+      <c r="P38" s="193"/>
+      <c r="Q38" s="193"/>
+      <c r="R38" s="194"/>
       <c r="S38" s="80"/>
     </row>
     <row r="39" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="79"/>
-      <c r="C39" s="221"/>
-      <c r="D39" s="219"/>
-      <c r="E39" s="219"/>
-      <c r="F39" s="219"/>
-      <c r="G39" s="219"/>
-      <c r="H39" s="219"/>
-      <c r="I39" s="219"/>
-      <c r="J39" s="219"/>
-      <c r="K39" s="219"/>
-      <c r="L39" s="219"/>
-      <c r="M39" s="219"/>
-      <c r="N39" s="219"/>
-      <c r="O39" s="219"/>
-      <c r="P39" s="219"/>
-      <c r="Q39" s="219"/>
-      <c r="R39" s="220"/>
+      <c r="C39" s="195"/>
+      <c r="D39" s="193"/>
+      <c r="E39" s="193"/>
+      <c r="F39" s="193"/>
+      <c r="G39" s="193"/>
+      <c r="H39" s="193"/>
+      <c r="I39" s="193"/>
+      <c r="J39" s="193"/>
+      <c r="K39" s="193"/>
+      <c r="L39" s="193"/>
+      <c r="M39" s="193"/>
+      <c r="N39" s="193"/>
+      <c r="O39" s="193"/>
+      <c r="P39" s="193"/>
+      <c r="Q39" s="193"/>
+      <c r="R39" s="194"/>
       <c r="S39" s="80"/>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="79"/>
-      <c r="C40" s="221"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
-      <c r="M40" s="219"/>
-      <c r="N40" s="219"/>
-      <c r="O40" s="219"/>
-      <c r="P40" s="219"/>
-      <c r="Q40" s="219"/>
-      <c r="R40" s="220"/>
+      <c r="C40" s="195"/>
+      <c r="D40" s="193"/>
+      <c r="E40" s="193"/>
+      <c r="F40" s="193"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
+      <c r="K40" s="193"/>
+      <c r="L40" s="193"/>
+      <c r="M40" s="193"/>
+      <c r="N40" s="193"/>
+      <c r="O40" s="193"/>
+      <c r="P40" s="193"/>
+      <c r="Q40" s="193"/>
+      <c r="R40" s="194"/>
       <c r="S40" s="80"/>
     </row>
     <row r="41" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B41" s="79"/>
-      <c r="C41" s="222"/>
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="223"/>
-      <c r="H41" s="223"/>
-      <c r="I41" s="223"/>
-      <c r="J41" s="223"/>
-      <c r="K41" s="223"/>
-      <c r="L41" s="223"/>
-      <c r="M41" s="223"/>
-      <c r="N41" s="223"/>
-      <c r="O41" s="223"/>
-      <c r="P41" s="223"/>
-      <c r="Q41" s="223"/>
-      <c r="R41" s="224"/>
+      <c r="C41" s="196"/>
+      <c r="D41" s="197"/>
+      <c r="E41" s="197"/>
+      <c r="F41" s="197"/>
+      <c r="G41" s="197"/>
+      <c r="H41" s="197"/>
+      <c r="I41" s="197"/>
+      <c r="J41" s="197"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="197"/>
+      <c r="N41" s="197"/>
+      <c r="O41" s="197"/>
+      <c r="P41" s="197"/>
+      <c r="Q41" s="197"/>
+      <c r="R41" s="198"/>
       <c r="S41" s="80"/>
     </row>
     <row r="42" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5537,22 +5552,62 @@
       <c r="S42" s="83"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hi9ZhV9bKTQaxNuT0jDfHOJ5L6xHqscZ8uQSl5hFAr+6F9Y5Iv+Ac5Qp0EDBTAj1wXEuE0P4U1loijcV5fxVxw==" saltValue="pLHbEaIUMf3+qd1EgYfymA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dwJ2ZG5RP+WgsIbnZse7/BsKh1CnMoIOzeADS1oIZHc2kw4e2AsUcQCY9kItX+iIev5OOAYiUyPoCZLQ4hljeg==" saltValue="nTbIqis5kT/d4y6YCOqxTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="84">
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="D32:M32"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="D15:Q15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="C8:R8"/>
+    <mergeCell ref="D10:Q10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="D19:M19"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
     <mergeCell ref="C36:R36"/>
     <mergeCell ref="C37:R41"/>
     <mergeCell ref="C24:R24"/>
@@ -5569,60 +5624,20 @@
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="D27:I27"/>
     <mergeCell ref="E28:I28"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="D19:M19"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="C2:R2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="C8:R8"/>
-    <mergeCell ref="D10:Q10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="D15:Q15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="D32:M32"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
   </mergeCells>
   <conditionalFormatting sqref="L21:M21">
     <cfRule type="expression" dxfId="10" priority="10">
@@ -6260,91 +6275,91 @@
       <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:603" ht="37.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="158"/>
-      <c r="B2" s="159" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="158" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="162"/>
-      <c r="M2" s="162"/>
-      <c r="N2" s="161"/>
-      <c r="O2" s="161"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="161"/>
-      <c r="S2" s="161"/>
-      <c r="T2" s="162"/>
-      <c r="U2" s="162"/>
-      <c r="V2" s="163" t="s">
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="160"/>
+      <c r="S2" s="160"/>
+      <c r="T2" s="161"/>
+      <c r="U2" s="161"/>
+      <c r="V2" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="W2" s="164"/>
-      <c r="X2" s="165"/>
-      <c r="Y2" s="165"/>
-      <c r="Z2" s="164"/>
-      <c r="AA2" s="164"/>
-      <c r="AB2" s="165"/>
-      <c r="AC2" s="165"/>
-      <c r="AD2" s="164"/>
-      <c r="AE2" s="164"/>
-      <c r="AF2" s="165"/>
-      <c r="AG2" s="165"/>
-      <c r="AH2" s="164"/>
-      <c r="AI2" s="164"/>
-      <c r="AJ2" s="165"/>
-      <c r="AK2" s="165"/>
-      <c r="AL2" s="164"/>
-      <c r="AM2" s="164"/>
-      <c r="AN2" s="165"/>
-      <c r="AO2" s="165"/>
-      <c r="AP2" s="164"/>
-      <c r="AQ2" s="164"/>
-      <c r="AR2" s="165"/>
-      <c r="AS2" s="165"/>
-      <c r="AT2" s="164"/>
-      <c r="AU2" s="164"/>
-      <c r="AV2" s="165"/>
-      <c r="AW2" s="165"/>
-      <c r="AX2" s="164"/>
-      <c r="AY2" s="164"/>
-      <c r="AZ2" s="165"/>
-      <c r="BA2" s="165"/>
-      <c r="BB2" s="164"/>
-      <c r="BC2" s="164"/>
-      <c r="BD2" s="165"/>
-      <c r="BE2" s="165"/>
-      <c r="BF2" s="166" t="s">
+      <c r="W2" s="163"/>
+      <c r="X2" s="164"/>
+      <c r="Y2" s="164"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="164"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="163"/>
+      <c r="AE2" s="163"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="164"/>
+      <c r="AH2" s="163"/>
+      <c r="AI2" s="163"/>
+      <c r="AJ2" s="164"/>
+      <c r="AK2" s="164"/>
+      <c r="AL2" s="163"/>
+      <c r="AM2" s="163"/>
+      <c r="AN2" s="164"/>
+      <c r="AO2" s="164"/>
+      <c r="AP2" s="163"/>
+      <c r="AQ2" s="163"/>
+      <c r="AR2" s="164"/>
+      <c r="AS2" s="164"/>
+      <c r="AT2" s="163"/>
+      <c r="AU2" s="163"/>
+      <c r="AV2" s="164"/>
+      <c r="AW2" s="164"/>
+      <c r="AX2" s="163"/>
+      <c r="AY2" s="163"/>
+      <c r="AZ2" s="164"/>
+      <c r="BA2" s="164"/>
+      <c r="BB2" s="163"/>
+      <c r="BC2" s="163"/>
+      <c r="BD2" s="164"/>
+      <c r="BE2" s="164"/>
+      <c r="BF2" s="165" t="s">
+        <v>303</v>
+      </c>
+      <c r="BG2" s="166"/>
+      <c r="BH2" s="166"/>
+      <c r="BI2" s="166"/>
+      <c r="BJ2" s="166"/>
+      <c r="BK2" s="166"/>
+      <c r="BL2" s="166"/>
+      <c r="BM2" s="166"/>
+      <c r="BN2" s="166"/>
+      <c r="BO2" s="166"/>
+      <c r="BP2" s="166"/>
+      <c r="BQ2" s="166"/>
+      <c r="BR2" s="167" t="s">
         <v>304</v>
       </c>
-      <c r="BG2" s="167"/>
-      <c r="BH2" s="167"/>
-      <c r="BI2" s="167"/>
-      <c r="BJ2" s="167"/>
-      <c r="BK2" s="167"/>
-      <c r="BL2" s="167"/>
-      <c r="BM2" s="167"/>
-      <c r="BN2" s="167"/>
-      <c r="BO2" s="167"/>
-      <c r="BP2" s="167"/>
-      <c r="BQ2" s="167"/>
-      <c r="BR2" s="168" t="s">
-        <v>305</v>
-      </c>
-      <c r="BS2" s="169"/>
-      <c r="BT2" s="169"/>
-      <c r="BU2" s="169"/>
-      <c r="BV2" s="169"/>
-      <c r="BW2" s="169"/>
-      <c r="BX2" s="169"/>
-      <c r="BY2" s="169"/>
+      <c r="BS2" s="168"/>
+      <c r="BT2" s="168"/>
+      <c r="BU2" s="168"/>
+      <c r="BV2" s="168"/>
+      <c r="BW2" s="168"/>
+      <c r="BX2" s="168"/>
+      <c r="BY2" s="168"/>
       <c r="LK2" s="19"/>
       <c r="MD2" s="19"/>
       <c r="MT2" s="19"/>
@@ -6394,7 +6409,7 @@
       <c r="H3" s="28"/>
       <c r="I3" s="29"/>
       <c r="J3" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K3" s="27"/>
       <c r="L3" s="28"/>
@@ -6406,7 +6421,7 @@
       <c r="P3" s="28"/>
       <c r="Q3" s="29"/>
       <c r="R3" s="27" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S3" s="27"/>
       <c r="T3" s="28"/>
@@ -6430,7 +6445,7 @@
       <c r="AF3" s="33"/>
       <c r="AG3" s="34"/>
       <c r="AH3" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AI3" s="32"/>
       <c r="AJ3" s="33"/>
@@ -6484,7 +6499,7 @@
       <c r="BP3" s="28"/>
       <c r="BQ3" s="29"/>
       <c r="BR3" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BS3" s="27"/>
       <c r="BT3" s="28"/>
@@ -6735,7 +6750,7 @@
         <v>119</v>
       </c>
       <c r="C5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D5" s="124">
         <v>10</v>
@@ -6747,7 +6762,7 @@
         <v>119</v>
       </c>
       <c r="G5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H5" s="124">
         <v>10</v>
@@ -6759,7 +6774,7 @@
         <v>119</v>
       </c>
       <c r="K5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L5" s="124">
         <v>10</v>
@@ -6771,7 +6786,7 @@
         <v>119</v>
       </c>
       <c r="O5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P5" s="124">
         <v>10</v>
@@ -6783,7 +6798,7 @@
         <v>119</v>
       </c>
       <c r="S5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T5" s="124">
         <v>10</v>
@@ -6795,7 +6810,7 @@
         <v>119</v>
       </c>
       <c r="W5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X5" s="124">
         <v>10</v>
@@ -6807,7 +6822,7 @@
         <v>119</v>
       </c>
       <c r="AA5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB5" s="124">
         <v>10</v>
@@ -6819,7 +6834,7 @@
         <v>119</v>
       </c>
       <c r="AE5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AF5" s="124">
         <v>10</v>
@@ -6831,7 +6846,7 @@
         <v>119</v>
       </c>
       <c r="AI5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AJ5" s="124">
         <v>10</v>
@@ -6843,7 +6858,7 @@
         <v>119</v>
       </c>
       <c r="AM5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AN5" s="124">
         <v>10</v>
@@ -6855,7 +6870,7 @@
         <v>119</v>
       </c>
       <c r="AQ5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AR5" s="124">
         <v>10</v>
@@ -6867,7 +6882,7 @@
         <v>119</v>
       </c>
       <c r="AU5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AV5" s="124">
         <v>10</v>
@@ -6879,7 +6894,7 @@
         <v>119</v>
       </c>
       <c r="AY5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ5" s="124">
         <v>10</v>
@@ -6891,7 +6906,7 @@
         <v>119</v>
       </c>
       <c r="BC5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BD5" s="124">
         <v>10</v>
@@ -6903,7 +6918,7 @@
         <v>119</v>
       </c>
       <c r="BG5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH5" s="124">
         <v>10</v>
@@ -6915,7 +6930,7 @@
         <v>119</v>
       </c>
       <c r="BK5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BL5" s="124">
         <v>10</v>
@@ -6927,7 +6942,7 @@
         <v>119</v>
       </c>
       <c r="BO5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BP5" s="124">
         <v>10</v>
@@ -6939,7 +6954,7 @@
         <v>119</v>
       </c>
       <c r="BS5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BT5" s="124">
         <v>10</v>
@@ -6951,7 +6966,7 @@
         <v>119</v>
       </c>
       <c r="BW5" s="123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BX5" s="124">
         <v>10</v>
@@ -6968,7 +6983,7 @@
         <v>120</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D6" s="42">
         <v>10</v>
@@ -6980,7 +6995,7 @@
         <v>120</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H6" s="42">
         <v>10</v>
@@ -6992,7 +7007,7 @@
         <v>120</v>
       </c>
       <c r="K6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L6" s="42">
         <v>10</v>
@@ -7004,7 +7019,7 @@
         <v>120</v>
       </c>
       <c r="O6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P6" s="42">
         <v>10</v>
@@ -7016,7 +7031,7 @@
         <v>120</v>
       </c>
       <c r="S6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T6" s="42">
         <v>10</v>
@@ -7028,7 +7043,7 @@
         <v>121</v>
       </c>
       <c r="W6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X6" s="42">
         <v>10</v>
@@ -7040,7 +7055,7 @@
         <v>121</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB6" s="42">
         <v>10</v>
@@ -7052,7 +7067,7 @@
         <v>23</v>
       </c>
       <c r="AE6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF6" s="42">
         <v>10</v>
@@ -7061,7 +7076,7 @@
         <v>39</v>
       </c>
       <c r="AH6" s="40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AI6" s="45"/>
       <c r="AJ6" s="42">
@@ -7071,7 +7086,7 @@
         <v>39</v>
       </c>
       <c r="AL6" s="40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AM6" s="45"/>
       <c r="AN6" s="42">
@@ -7084,7 +7099,7 @@
         <v>120</v>
       </c>
       <c r="AQ6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR6" s="42">
         <v>10</v>
@@ -7096,7 +7111,7 @@
         <v>122</v>
       </c>
       <c r="AU6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AV6" s="42">
         <v>10</v>
@@ -7105,10 +7120,10 @@
         <v>39</v>
       </c>
       <c r="AX6" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AY6" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ6" s="42">
         <v>10</v>
@@ -7120,7 +7135,7 @@
         <v>123</v>
       </c>
       <c r="BC6" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD6" s="42">
         <v>20</v>
@@ -7132,7 +7147,7 @@
         <v>24</v>
       </c>
       <c r="BG6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BH6" s="42">
         <v>15</v>
@@ -7154,7 +7169,7 @@
         <v>26</v>
       </c>
       <c r="BO6" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BP6" s="42">
         <v>20</v>
@@ -7163,10 +7178,10 @@
         <v>39</v>
       </c>
       <c r="BR6" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="BS6" s="41" t="s">
         <v>181</v>
-      </c>
-      <c r="BS6" s="41" t="s">
-        <v>182</v>
       </c>
       <c r="BT6" s="42">
         <v>30</v>
@@ -7175,10 +7190,10 @@
         <v>39</v>
       </c>
       <c r="BV6" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="BW6" s="41" t="s">
         <v>183</v>
-      </c>
-      <c r="BW6" s="41" t="s">
-        <v>184</v>
       </c>
       <c r="BX6" s="42">
         <v>20</v>
@@ -7195,7 +7210,7 @@
         <v>124</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D7" s="131">
         <v>10</v>
@@ -7207,7 +7222,7 @@
         <v>124</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H7" s="131">
         <v>10</v>
@@ -7219,7 +7234,7 @@
         <v>124</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L7" s="131">
         <v>10</v>
@@ -7231,7 +7246,7 @@
         <v>124</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P7" s="131">
         <v>10</v>
@@ -7243,7 +7258,7 @@
         <v>124</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T7" s="131">
         <v>10</v>
@@ -7252,7 +7267,7 @@
         <v>39</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W7" s="25" t="s">
         <v>125</v>
@@ -7264,7 +7279,7 @@
         <v>39</v>
       </c>
       <c r="Z7" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA7" s="25" t="s">
         <v>125</v>
@@ -7276,10 +7291,10 @@
         <v>39</v>
       </c>
       <c r="AD7" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AE7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF7" s="131">
         <v>10</v>
@@ -7288,14 +7303,14 @@
         <v>39</v>
       </c>
       <c r="AH7" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AI7" s="25"/>
       <c r="AJ7" s="131">
         <v>10</v>
       </c>
       <c r="AK7" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL7" s="24" t="s">
         <v>126</v>
@@ -7305,13 +7320,13 @@
         <v>10</v>
       </c>
       <c r="AO7" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP7" s="24" t="s">
         <v>127</v>
       </c>
       <c r="AQ7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR7" s="131">
         <v>10</v>
@@ -7323,7 +7338,7 @@
         <v>128</v>
       </c>
       <c r="AU7" s="133" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AV7" s="131">
         <v>10</v>
@@ -7335,25 +7350,25 @@
         <v>129</v>
       </c>
       <c r="AY7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ7" s="131">
         <v>10</v>
       </c>
       <c r="BA7" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB7" s="24" t="s">
         <v>130</v>
       </c>
       <c r="BC7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD7" s="131">
         <v>20</v>
       </c>
       <c r="BE7" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF7" s="24" t="s">
         <v>131</v>
@@ -7383,7 +7398,7 @@
         <v>133</v>
       </c>
       <c r="BO7" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BP7" s="131">
         <v>30</v>
@@ -7392,7 +7407,7 @@
         <v>39</v>
       </c>
       <c r="BR7" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BS7" s="25" t="s">
         <v>137</v>
@@ -7404,10 +7419,10 @@
         <v>39</v>
       </c>
       <c r="BV7" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BW7" s="25" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BX7" s="131">
         <v>20</v>
@@ -7442,7 +7457,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J8" s="40" t="s">
         <v>134</v>
@@ -7574,13 +7589,13 @@
         <v>10</v>
       </c>
       <c r="BA8" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB8" s="40" t="s">
         <v>139</v>
       </c>
       <c r="BC8" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD8" s="42">
         <v>20</v>
@@ -7592,7 +7607,7 @@
         <v>27</v>
       </c>
       <c r="BG8" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BH8" s="42">
         <v>5</v>
@@ -7623,10 +7638,10 @@
         <v>39</v>
       </c>
       <c r="BR8" s="44" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BS8" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BT8" s="42">
         <v>30</v>
@@ -7635,7 +7650,7 @@
         <v>39</v>
       </c>
       <c r="BV8" s="40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BW8" s="41" t="s">
         <v>137</v>
@@ -7661,7 +7676,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="137" t="s">
         <v>143</v>
@@ -7673,7 +7688,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="137" t="s">
         <v>141</v>
@@ -7685,7 +7700,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N9" s="137" t="s">
         <v>141</v>
@@ -7697,7 +7712,7 @@
         <v>20</v>
       </c>
       <c r="Q9" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R9" s="137" t="s">
         <v>141</v>
@@ -7709,13 +7724,13 @@
         <v>20</v>
       </c>
       <c r="U9" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V9" s="10" t="s">
         <v>33</v>
       </c>
       <c r="W9" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X9" s="131">
         <v>10</v>
@@ -7727,7 +7742,7 @@
         <v>33</v>
       </c>
       <c r="AA9" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AB9" s="131">
         <v>10</v>
@@ -7739,7 +7754,7 @@
         <v>33</v>
       </c>
       <c r="AE9" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AF9" s="131">
         <v>10</v>
@@ -7751,7 +7766,7 @@
         <v>144</v>
       </c>
       <c r="AI9" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AJ9" s="131">
         <v>10</v>
@@ -7763,7 +7778,7 @@
         <v>144</v>
       </c>
       <c r="AM9" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AN9" s="131">
         <v>10</v>
@@ -7811,7 +7826,7 @@
         <v>149</v>
       </c>
       <c r="BC9" s="133" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD9" s="131">
         <v>20</v>
@@ -7829,7 +7844,7 @@
         <v>5</v>
       </c>
       <c r="BI9" s="134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ9" s="135" t="s">
         <v>150</v>
@@ -7841,13 +7856,13 @@
         <v>5</v>
       </c>
       <c r="BM9" s="136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN9" s="137" t="s">
         <v>152</v>
       </c>
       <c r="BO9" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BP9" s="139">
         <v>20</v>
@@ -7856,20 +7871,20 @@
         <v>39</v>
       </c>
       <c r="BR9" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="BS9" s="138" t="s">
+        <v>241</v>
+      </c>
+      <c r="BT9" s="139"/>
+      <c r="BU9" s="149" t="s">
         <v>242</v>
       </c>
-      <c r="BS9" s="138" t="s">
-        <v>242</v>
-      </c>
-      <c r="BT9" s="139"/>
-      <c r="BU9" s="150" t="s">
-        <v>243</v>
-      </c>
       <c r="BV9" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BW9" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BX9" s="131">
         <v>30</v>
@@ -7883,70 +7898,70 @@
         <v>6</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D10" s="49">
         <v>20</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H10" s="49">
         <v>20</v>
       </c>
       <c r="I10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J10" s="47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K10" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L10" s="49">
         <v>20</v>
       </c>
       <c r="M10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P10" s="49">
         <v>20</v>
       </c>
       <c r="Q10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R10" s="47" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S10" s="48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T10" s="49">
         <v>20</v>
       </c>
       <c r="U10" s="50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V10" s="44" t="s">
         <v>153</v>
       </c>
       <c r="W10" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X10" s="42">
         <v>10</v>
@@ -7958,7 +7973,7 @@
         <v>154</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB10" s="42">
         <v>10</v>
@@ -7967,10 +7982,10 @@
         <v>39</v>
       </c>
       <c r="AD10" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AE10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF10" s="42">
         <v>10</v>
@@ -7979,7 +7994,7 @@
         <v>39</v>
       </c>
       <c r="AH10" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AI10" s="41"/>
       <c r="AJ10" s="42">
@@ -7989,7 +8004,7 @@
         <v>39</v>
       </c>
       <c r="AL10" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AM10" s="41"/>
       <c r="AN10" s="42">
@@ -7999,10 +8014,10 @@
         <v>39</v>
       </c>
       <c r="AP10" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AQ10" s="45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR10" s="42">
         <v>10</v>
@@ -8011,10 +8026,10 @@
         <v>39</v>
       </c>
       <c r="AT10" s="40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AU10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AV10" s="42">
         <v>10</v>
@@ -8026,25 +8041,25 @@
         <v>155</v>
       </c>
       <c r="AY10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ10" s="42">
         <v>20</v>
       </c>
       <c r="BA10" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB10" s="40" t="s">
         <v>156</v>
       </c>
       <c r="BC10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD10" s="42">
         <v>5</v>
       </c>
       <c r="BE10" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF10" s="40" t="s">
         <v>34</v>
@@ -8056,13 +8071,13 @@
         <v>5</v>
       </c>
       <c r="BI10" s="109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ10" s="110" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BK10" s="41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BL10" s="42">
         <v>0</v>
@@ -8071,34 +8086,34 @@
         <v>39</v>
       </c>
       <c r="BN10" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="BO10" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="BP10" s="42"/>
+      <c r="BQ10" s="150" t="s">
         <v>242</v>
       </c>
-      <c r="BO10" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="BP10" s="42"/>
-      <c r="BQ10" s="151" t="s">
-        <v>243</v>
-      </c>
       <c r="BR10" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BS10" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BT10" s="42"/>
       <c r="BU10" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BV10" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="BW10" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="BX10" s="42"/>
+      <c r="BY10" s="150" t="s">
         <v>242</v>
-      </c>
-      <c r="BW10" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="BX10" s="42"/>
-      <c r="BY10" s="151" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:603" s="23" customFormat="1" ht="140.35" x14ac:dyDescent="0.4">
@@ -8106,178 +8121,178 @@
         <v>7</v>
       </c>
       <c r="B11" s="137" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D11" s="139">
         <v>20</v>
       </c>
       <c r="E11" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="137" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G11" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H11" s="139">
         <v>20</v>
       </c>
       <c r="I11" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11" s="137" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K11" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L11" s="139">
         <v>20</v>
       </c>
       <c r="M11" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N11" s="137" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O11" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P11" s="139">
         <v>20</v>
       </c>
       <c r="Q11" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R11" s="137" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S11" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T11" s="139">
         <v>20</v>
       </c>
       <c r="U11" s="140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="W11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X11" s="131">
         <v>10</v>
       </c>
       <c r="Y11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="AA11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB11" s="131">
         <v>10</v>
       </c>
       <c r="AC11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="AE11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF11" s="131">
         <v>10</v>
       </c>
       <c r="AG11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="AI11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ11" s="131">
         <v>10</v>
       </c>
       <c r="AK11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="AM11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN11" s="131">
         <v>10</v>
       </c>
       <c r="AO11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP11" s="10" t="s">
         <v>158</v>
       </c>
       <c r="AQ11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR11" s="131">
         <v>10</v>
       </c>
       <c r="AS11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT11" s="24" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AU11" s="133" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AV11" s="131">
         <v>15</v>
       </c>
       <c r="AW11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>159</v>
       </c>
       <c r="AY11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ11" s="131">
         <v>20</v>
       </c>
       <c r="BA11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BB11" s="24" t="s">
         <v>160</v>
       </c>
       <c r="BC11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD11" s="131">
         <v>5</v>
       </c>
       <c r="BE11" s="132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BF11" s="24" t="s">
         <v>157</v>
       </c>
       <c r="BG11" s="25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BH11" s="131">
         <v>10</v>
@@ -8285,47 +8300,47 @@
       <c r="BI11" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="BJ11" s="170" t="s">
-        <v>307</v>
-      </c>
-      <c r="BK11" s="171" t="s">
-        <v>239</v>
-      </c>
-      <c r="BL11" s="172">
+      <c r="BJ11" s="169" t="s">
+        <v>306</v>
+      </c>
+      <c r="BK11" s="170" t="s">
+        <v>238</v>
+      </c>
+      <c r="BL11" s="171">
         <v>10</v>
       </c>
-      <c r="BM11" s="173" t="s">
-        <v>40</v>
+      <c r="BM11" s="136" t="s">
+        <v>39</v>
       </c>
       <c r="BN11" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BO11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BP11" s="131"/>
       <c r="BQ11" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BR11" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="BS11" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="BT11" s="131"/>
+      <c r="BU11" s="151" t="s">
         <v>242</v>
       </c>
-      <c r="BS11" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="BT11" s="131"/>
-      <c r="BU11" s="152" t="s">
-        <v>243</v>
-      </c>
       <c r="BV11" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW11" s="25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BX11" s="131"/>
       <c r="BY11" s="132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:603" s="46" customFormat="1" ht="178.35" x14ac:dyDescent="0.4">
@@ -8342,7 +8357,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="40" t="s">
         <v>161</v>
@@ -8354,7 +8369,7 @@
         <v>10</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" s="51" t="s">
         <v>161</v>
@@ -8366,7 +8381,7 @@
         <v>10</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N12" s="51" t="s">
         <v>161</v>
@@ -8378,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R12" s="51" t="s">
         <v>161</v>
@@ -8390,91 +8405,91 @@
         <v>10</v>
       </c>
       <c r="U12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="W12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X12" s="42">
         <v>10</v>
       </c>
       <c r="Y12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="AA12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB12" s="42">
         <v>10</v>
       </c>
       <c r="AC12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="AE12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AF12" s="42">
         <v>10</v>
       </c>
       <c r="AG12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="AI12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AJ12" s="42">
         <v>10</v>
       </c>
       <c r="AK12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="AM12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AN12" s="42">
         <v>10</v>
       </c>
       <c r="AO12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP12" s="44" t="s">
         <v>163</v>
       </c>
       <c r="AQ12" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AR12" s="42">
         <v>10</v>
       </c>
       <c r="AS12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT12" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="AU12" s="41" t="s">
         <v>300</v>
-      </c>
-      <c r="AU12" s="41" t="s">
-        <v>301</v>
       </c>
       <c r="AV12" s="42">
         <v>15</v>
       </c>
       <c r="AW12" s="43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AX12" s="47" t="s">
         <v>164</v>
@@ -8485,72 +8500,72 @@
       <c r="AZ12" s="49">
         <v>20</v>
       </c>
-      <c r="BA12" s="50" t="s">
-        <v>40</v>
+      <c r="BA12" s="43" t="s">
+        <v>39</v>
       </c>
       <c r="BB12" s="40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BC12" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD12" s="42"/>
       <c r="BE12" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BF12" s="40" t="s">
         <v>35</v>
       </c>
       <c r="BG12" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BH12" s="42">
         <v>5</v>
       </c>
       <c r="BI12" s="109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BJ12" s="110" t="s">
         <v>35</v>
       </c>
       <c r="BK12" s="41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BL12" s="42">
         <v>5</v>
       </c>
       <c r="BM12" s="111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN12" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="BO12" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="BP12" s="42"/>
+      <c r="BQ12" s="152" t="s">
         <v>242</v>
       </c>
-      <c r="BO12" s="41" t="s">
+      <c r="BR12" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="BS12" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="BT12" s="42"/>
+      <c r="BU12" s="150" t="s">
         <v>242</v>
       </c>
-      <c r="BP12" s="42"/>
-      <c r="BQ12" s="153" t="s">
-        <v>243</v>
-      </c>
-      <c r="BR12" s="44" t="s">
+      <c r="BV12" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="BW12" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="BX12" s="42"/>
+      <c r="BY12" s="153" t="s">
         <v>242</v>
-      </c>
-      <c r="BS12" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="BT12" s="42"/>
-      <c r="BU12" s="151" t="s">
-        <v>243</v>
-      </c>
-      <c r="BV12" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="BW12" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="BX12" s="42"/>
-      <c r="BY12" s="154" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:603" s="23" customFormat="1" ht="93.35" x14ac:dyDescent="0.4">
@@ -8561,7 +8576,7 @@
         <v>36</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="14">
         <v>20</v>
@@ -8573,7 +8588,7 @@
         <v>36</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H13" s="14">
         <v>20</v>
@@ -8585,7 +8600,7 @@
         <v>36</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L13" s="14">
         <v>20</v>
@@ -8597,7 +8612,7 @@
         <v>36</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P13" s="14">
         <v>20</v>
@@ -8606,10 +8621,10 @@
         <v>38</v>
       </c>
       <c r="R13" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T13" s="14">
         <v>20</v>
@@ -8627,7 +8642,7 @@
         <v>10</v>
       </c>
       <c r="Y13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z13" s="143" t="s">
         <v>167</v>
@@ -8639,7 +8654,7 @@
         <v>10</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD13" s="143" t="s">
         <v>167</v>
@@ -8651,7 +8666,7 @@
         <v>10</v>
       </c>
       <c r="AG13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AH13" s="143" t="s">
         <v>167</v>
@@ -8663,7 +8678,7 @@
         <v>10</v>
       </c>
       <c r="AK13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AL13" s="143" t="s">
         <v>167</v>
@@ -8675,7 +8690,7 @@
         <v>10</v>
       </c>
       <c r="AO13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AP13" s="143" t="s">
         <v>167</v>
@@ -8687,95 +8702,95 @@
         <v>10</v>
       </c>
       <c r="AS13" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AT13" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AU13" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AV13" s="14">
         <v>0</v>
       </c>
       <c r="AW13" s="15" t="s">
-        <v>38</v>
+        <v>242</v>
       </c>
       <c r="AX13" s="144" t="s">
         <v>170</v>
       </c>
       <c r="AY13" s="145" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ13" s="146">
         <v>20</v>
       </c>
-      <c r="BA13" s="147" t="s">
-        <v>40</v>
+      <c r="BA13" s="132" t="s">
+        <v>39</v>
       </c>
       <c r="BB13" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BC13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD13" s="14"/>
       <c r="BE13" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BF13" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="BG13" s="148" t="s">
-        <v>242</v>
+      <c r="BG13" s="147" t="s">
+        <v>241</v>
       </c>
       <c r="BH13" s="14">
         <v>15</v>
       </c>
-      <c r="BI13" s="149" t="s">
-        <v>40</v>
-      </c>
-      <c r="BJ13" s="174" t="s">
+      <c r="BI13" s="148" t="s">
+        <v>39</v>
+      </c>
+      <c r="BJ13" s="172" t="s">
         <v>166</v>
       </c>
-      <c r="BK13" s="175" t="s">
+      <c r="BK13" s="173" t="s">
+        <v>241</v>
+      </c>
+      <c r="BL13" s="174">
+        <v>15</v>
+      </c>
+      <c r="BM13" s="136" t="s">
+        <v>39</v>
+      </c>
+      <c r="BN13" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="BO13" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="BP13" s="14"/>
+      <c r="BQ13" s="151" t="s">
         <v>242</v>
       </c>
-      <c r="BL13" s="176">
-        <v>15</v>
-      </c>
-      <c r="BM13" s="177" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN13" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="BO13" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="BP13" s="14"/>
-      <c r="BQ13" s="152" t="s">
-        <v>243</v>
-      </c>
       <c r="BR13" s="143" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BS13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BT13" s="14"/>
       <c r="BU13" s="132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BV13" s="143" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BW13" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BX13" s="14"/>
       <c r="BY13" s="132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:603" s="46" customFormat="1" ht="38.35" thickBot="1" x14ac:dyDescent="0.45">
@@ -8783,60 +8798,60 @@
         <v>10</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" s="55"/>
       <c r="E14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H14" s="55"/>
       <c r="I14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L14" s="55"/>
       <c r="M14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P14" s="55"/>
       <c r="Q14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T14" s="55"/>
       <c r="U14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V14" s="57" t="s">
         <v>169</v>
       </c>
       <c r="W14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="X14" s="55">
         <v>10</v>
@@ -8848,7 +8863,7 @@
         <v>169</v>
       </c>
       <c r="AA14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB14" s="55">
         <v>10</v>
@@ -8860,7 +8875,7 @@
         <v>169</v>
       </c>
       <c r="AE14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF14" s="55">
         <v>10</v>
@@ -8872,7 +8887,7 @@
         <v>169</v>
       </c>
       <c r="AI14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ14" s="55">
         <v>10</v>
@@ -8884,7 +8899,7 @@
         <v>169</v>
       </c>
       <c r="AM14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN14" s="55">
         <v>10</v>
@@ -8896,7 +8911,7 @@
         <v>169</v>
       </c>
       <c r="AQ14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AR14" s="55">
         <v>10</v>
@@ -8905,22 +8920,22 @@
         <v>38</v>
       </c>
       <c r="AT14" s="53" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AU14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AV14" s="55">
         <v>10</v>
       </c>
       <c r="AW14" s="56" t="s">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="AX14" s="53" t="s">
         <v>171</v>
       </c>
       <c r="AY14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AZ14" s="55">
         <v>10</v>
@@ -8929,68 +8944,68 @@
         <v>38</v>
       </c>
       <c r="BB14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BC14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BD14" s="55"/>
       <c r="BE14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BF14" s="53" t="s">
         <v>37</v>
       </c>
       <c r="BG14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BH14" s="55">
         <v>25</v>
       </c>
       <c r="BI14" s="112" t="s">
-        <v>40</v>
-      </c>
-      <c r="BJ14" s="155" t="s">
+        <v>39</v>
+      </c>
+      <c r="BJ14" s="154" t="s">
         <v>37</v>
       </c>
       <c r="BK14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BL14" s="55">
         <v>30</v>
       </c>
-      <c r="BM14" s="156" t="s">
-        <v>243</v>
+      <c r="BM14" s="155" t="s">
+        <v>39</v>
       </c>
       <c r="BN14" s="53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BO14" s="54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BP14" s="55"/>
       <c r="BQ14" s="56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BR14" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="BS14" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="BT14" s="55"/>
+      <c r="BU14" s="156" t="s">
         <v>242</v>
       </c>
-      <c r="BS14" s="54" t="s">
+      <c r="BV14" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="BW14" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="BX14" s="55"/>
+      <c r="BY14" s="156" t="s">
         <v>242</v>
-      </c>
-      <c r="BT14" s="55"/>
-      <c r="BU14" s="157" t="s">
-        <v>243</v>
-      </c>
-      <c r="BV14" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="BW14" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="BX14" s="55"/>
-      <c r="BY14" s="157" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:603" s="11" customFormat="1" x14ac:dyDescent="0.4">
@@ -16916,7 +16931,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LQMtKq4u3SZ3dWG40l6cNSz8DcSFM64Y4sgz55qgAQx0IZGc1ZqZCrvkq9Rz59W7Nwq/SA5eBCtyJ7SJGvzE0A==" saltValue="cLd5StC2DkxbwF8AwNEjAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NuOFOq/VHgCRz18NRZmm0y6s/ZSnveytFE+W9jC1blzo4YwEDkWO1ZnA4ZVKSUiYfZkgejj0a7SaxRa5B9q6Qg==" saltValue="l58riu/oPCDAyDRkLQ2DpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16961,10 +16976,10 @@
       <c r="H3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="245" t="s">
-        <v>246</v>
-      </c>
-      <c r="J3" s="246"/>
+      <c r="I3" s="246" t="s">
+        <v>245</v>
+      </c>
+      <c r="J3" s="247"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -16995,7 +17010,7 @@
         <v>48</v>
       </c>
       <c r="J4" s="114" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
@@ -17027,7 +17042,7 @@
         <v>45</v>
       </c>
       <c r="J5" s="114" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
@@ -17053,7 +17068,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="115" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
@@ -17061,7 +17076,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>56</v>
@@ -17073,7 +17088,7 @@
         <v>56</v>
       </c>
       <c r="J7" s="115" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -17091,12 +17106,12 @@
         <v>59</v>
       </c>
       <c r="J8" s="115" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>60</v>
@@ -17109,7 +17124,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
@@ -17124,7 +17139,7 @@
         <v>63</v>
       </c>
       <c r="J10" s="114" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
@@ -17138,7 +17153,7 @@
         <v>46</v>
       </c>
       <c r="J11" s="114" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
@@ -17152,7 +17167,7 @@
         <v>55</v>
       </c>
       <c r="J12" s="114" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
@@ -17166,7 +17181,7 @@
         <v>64</v>
       </c>
       <c r="J13" s="114" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
@@ -17180,7 +17195,7 @@
         <v>67</v>
       </c>
       <c r="J14" s="114" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
@@ -17194,7 +17209,7 @@
         <v>65</v>
       </c>
       <c r="J15" s="114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
@@ -17202,10 +17217,10 @@
         <v>49</v>
       </c>
       <c r="I16" s="116" t="s">
+        <v>257</v>
+      </c>
+      <c r="J16" s="117" t="s">
         <v>258</v>
-      </c>
-      <c r="J16" s="117" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
@@ -17213,10 +17228,10 @@
         <v>51</v>
       </c>
       <c r="I17" s="116" t="s">
+        <v>259</v>
+      </c>
+      <c r="J17" s="117" t="s">
         <v>260</v>
-      </c>
-      <c r="J17" s="117" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
@@ -17224,10 +17239,10 @@
         <v>63</v>
       </c>
       <c r="I18" s="116" t="s">
+        <v>261</v>
+      </c>
+      <c r="J18" s="117" t="s">
         <v>262</v>
-      </c>
-      <c r="J18" s="117" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
@@ -17235,10 +17250,10 @@
         <v>70</v>
       </c>
       <c r="I19" s="116" t="s">
+        <v>263</v>
+      </c>
+      <c r="J19" s="117" t="s">
         <v>264</v>
-      </c>
-      <c r="J19" s="117" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
@@ -17259,14 +17274,16 @@
         <v>41</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>243</v>
-      </c>
-      <c r="H20" s="1"/>
+        <v>242</v>
+      </c>
+      <c r="H20" s="248" t="s">
+        <v>307</v>
+      </c>
       <c r="I20" s="116" t="s">
+        <v>265</v>
+      </c>
+      <c r="J20" s="117" t="s">
         <v>266</v>
-      </c>
-      <c r="J20" s="117" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
@@ -17279,21 +17296,23 @@
       <c r="C21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>244</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>243</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I21" s="116" t="s">
+        <v>267</v>
+      </c>
+      <c r="J21" s="117" t="s">
         <v>268</v>
-      </c>
-      <c r="J21" s="117" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
@@ -17306,23 +17325,25 @@
       <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
+      <c r="D22" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="1"/>
+      <c r="H22" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="I22" s="116" t="s">
         <v>66</v>
       </c>
       <c r="J22" s="117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>11</v>
@@ -17330,78 +17351,75 @@
       <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
+      <c r="D23" s="3" t="s">
+        <v>309</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="1"/>
+      <c r="H23" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I23" s="113" t="s">
         <v>69</v>
       </c>
       <c r="J23" s="114" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>244</v>
+      <c r="B24" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="116" t="s">
+        <v>271</v>
+      </c>
+      <c r="J24" s="117" t="s">
         <v>272</v>
-      </c>
-      <c r="J24" s="117" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C25" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" t="s">
-        <v>244</v>
+      <c r="C25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="I25" s="116" t="s">
+        <v>273</v>
+      </c>
+      <c r="J25" s="117" t="s">
         <v>274</v>
-      </c>
-      <c r="J25" s="117" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D26" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="D26" s="1"/>
       <c r="I26" s="113" t="s">
         <v>62</v>
       </c>
       <c r="J26" s="114" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="D27" t="s">
-        <v>244</v>
-      </c>
       <c r="I27" s="116" t="s">
+        <v>275</v>
+      </c>
+      <c r="J27" s="117" t="s">
         <v>276</v>
-      </c>
-      <c r="J27" s="117" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
@@ -17411,10 +17429,10 @@
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
       <c r="I28" s="116" t="s">
+        <v>277</v>
+      </c>
+      <c r="J28" s="117" t="s">
         <v>278</v>
-      </c>
-      <c r="J28" s="117" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
@@ -17425,13 +17443,19 @@
         <v>91</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>292</v>
+        <v>291</v>
+      </c>
+      <c r="D29" s="249" t="s">
+        <v>310</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>311</v>
       </c>
       <c r="I29" s="113" t="s">
         <v>70</v>
       </c>
       <c r="J29" s="114" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
@@ -17442,13 +17466,19 @@
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>293</v>
+        <v>292</v>
+      </c>
+      <c r="D30" s="250" t="s">
+        <v>312</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="I30" s="113" t="s">
         <v>49</v>
       </c>
       <c r="J30" s="118" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
@@ -17459,30 +17489,36 @@
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>293</v>
+      </c>
+      <c r="D31" s="250" t="s">
+        <v>314</v>
       </c>
       <c r="I31" s="113" t="s">
         <v>51</v>
       </c>
       <c r="J31" s="114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>294</v>
+      </c>
+      <c r="D32" s="250" t="s">
+        <v>315</v>
       </c>
       <c r="I32" s="113" t="s">
         <v>54</v>
       </c>
       <c r="J32" s="114" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
@@ -17490,18 +17526,18 @@
         <v>89</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I33" s="119" t="s">
         <v>57</v>
       </c>
       <c r="J33" s="120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>17</v>
@@ -17530,9 +17566,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="9" t="s">
-        <v>68</v>
-      </c>
+      <c r="B39" s="9"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" s="58" t="s">
@@ -17587,8 +17621,8 @@
       <c r="F44" t="s">
         <v>173</v>
       </c>
-      <c r="G44" t="s">
-        <v>179</v>
+      <c r="G44" s="251" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.4">
@@ -17610,7 +17644,7 @@
       <c r="F45" t="s">
         <v>174</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="251" t="s">
         <v>82</v>
       </c>
     </row>
@@ -17633,7 +17667,7 @@
       <c r="F46" t="s">
         <v>172</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="251" t="s">
         <v>178</v>
       </c>
     </row>
@@ -17647,6 +17681,9 @@
       <c r="E47" t="s">
         <v>109</v>
       </c>
+      <c r="G47" s="251" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="C48" t="s">
@@ -17673,12 +17710,12 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" s="100" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" s="101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="61" t="s">
         <v>74</v>
@@ -17686,32 +17723,32 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" s="102" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1MxSPBFMde9JIRLWOPvU43L0QdXjOahuzb5lpDZhGe0jH8V1TF4lLAW7nRlKmS4mza+bL34d5MsGJIH87I7p8g==" saltValue="lhvCuzcF+p495iSxI4kDiA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fhUqCP4nmdi7Ah7W+hh8CW3bHAFN48Bq7+w8qbJag7STQFRIWMrmhP1Ys2PMI16GsYd9Rar5xNrcWtI/K68kew==" saltValue="RNNMmb2vcLdOzQWgDKCpFw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -17720,36 +17757,41 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A21:A23">
-    <cfRule type="expression" priority="12">
+    <cfRule type="expression" priority="13">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:D9">
-    <cfRule type="expression" priority="13">
+    <cfRule type="expression" priority="14">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
-    <cfRule type="expression" priority="86">
+    <cfRule type="expression" priority="87">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30:I33">
+    <cfRule type="expression" priority="3">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
+    <cfRule type="expression" priority="4">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:J29">
+    <cfRule type="expression" priority="5">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J33">
     <cfRule type="expression" priority="2">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:J5 I6:I8 I9:J13 I15:J21">
-    <cfRule type="expression" priority="3">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I23:J29">
-    <cfRule type="expression" priority="4">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J33">
+  <conditionalFormatting sqref="H21:H22">
     <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
@@ -17760,6 +17802,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -17962,22 +18019,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17994,29 +18061,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/AutosurveillanceTemplates/THERMO.xlsx
+++ b/AutosurveillanceTemplates/THERMO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C2AE19-E46F-4158-B6DB-431425A84629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A89755-A9F4-41CA-9156-BB22807FA97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20595" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,8 +61,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="318">
   <si>
     <t>Pluviomètre</t>
   </si>
@@ -3348,7 +3370,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3866,6 +3888,12 @@
     <xf numFmtId="165" fontId="34" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4012,6 +4040,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -4103,12 +4134,6 @@
     <xf numFmtId="0" fontId="38" fillId="9" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4555,131 +4580,131 @@
     </row>
     <row r="2" spans="2:19" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B2" s="66"/>
-      <c r="C2" s="217" t="s">
+      <c r="C2" s="221" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="218"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="219"/>
+      <c r="D2" s="222"/>
+      <c r="E2" s="222"/>
+      <c r="F2" s="222"/>
+      <c r="G2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
+      <c r="N2" s="222"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="223"/>
       <c r="S2" s="67"/>
     </row>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="68"/>
-      <c r="C3" s="220" t="s">
+      <c r="C3" s="224" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="221"/>
-      <c r="E3" s="222"/>
-      <c r="F3" s="222"/>
-      <c r="G3" s="222"/>
-      <c r="H3" s="221" t="s">
+      <c r="D3" s="225"/>
+      <c r="E3" s="226"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="226"/>
+      <c r="H3" s="225" t="s">
         <v>210</v>
       </c>
-      <c r="I3" s="221"/>
-      <c r="J3" s="222"/>
-      <c r="K3" s="222"/>
-      <c r="L3" s="222"/>
-      <c r="M3" s="221" t="s">
+      <c r="I3" s="225"/>
+      <c r="J3" s="227"/>
+      <c r="K3" s="227"/>
+      <c r="L3" s="227"/>
+      <c r="M3" s="225" t="s">
         <v>212</v>
       </c>
-      <c r="N3" s="221"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="215"/>
-      <c r="Q3" s="215"/>
-      <c r="R3" s="216"/>
+      <c r="N3" s="225"/>
+      <c r="O3" s="225"/>
+      <c r="P3" s="219"/>
+      <c r="Q3" s="219"/>
+      <c r="R3" s="220"/>
       <c r="S3" s="69"/>
     </row>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="68"/>
-      <c r="C4" s="220" t="s">
+      <c r="C4" s="224" t="s">
         <v>207</v>
       </c>
-      <c r="D4" s="221"/>
-      <c r="E4" s="222"/>
-      <c r="F4" s="222"/>
-      <c r="G4" s="222"/>
-      <c r="H4" s="221" t="s">
+      <c r="D4" s="225"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="225" t="s">
         <v>215</v>
       </c>
-      <c r="I4" s="221"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="222"/>
-      <c r="L4" s="222"/>
-      <c r="M4" s="221" t="s">
+      <c r="I4" s="225"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="227"/>
+      <c r="L4" s="227"/>
+      <c r="M4" s="225" t="s">
         <v>217</v>
       </c>
-      <c r="N4" s="221"/>
-      <c r="O4" s="221"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="216"/>
+      <c r="N4" s="225"/>
+      <c r="O4" s="225"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="220"/>
       <c r="S4" s="69"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="68"/>
-      <c r="C5" s="220" t="s">
+      <c r="C5" s="224" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="221"/>
-      <c r="E5" s="222"/>
-      <c r="F5" s="222"/>
-      <c r="G5" s="222"/>
-      <c r="H5" s="221" t="s">
+      <c r="D5" s="225"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="225" t="s">
         <v>216</v>
       </c>
-      <c r="I5" s="221"/>
-      <c r="J5" s="222"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="222"/>
-      <c r="M5" s="221" t="s">
+      <c r="I5" s="225"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="M5" s="225" t="s">
         <v>213</v>
       </c>
-      <c r="N5" s="221"/>
-      <c r="O5" s="221"/>
-      <c r="P5" s="225"/>
-      <c r="Q5" s="225"/>
-      <c r="R5" s="226"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="230"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="231"/>
       <c r="S5" s="69"/>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="68"/>
-      <c r="C6" s="227" t="s">
+      <c r="C6" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="D6" s="228"/>
-      <c r="E6" s="229"/>
-      <c r="F6" s="229"/>
-      <c r="G6" s="229"/>
-      <c r="H6" s="228" t="s">
+      <c r="D6" s="233"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="234"/>
+      <c r="G6" s="234"/>
+      <c r="H6" s="233" t="s">
         <v>211</v>
       </c>
-      <c r="I6" s="228"/>
-      <c r="J6" s="229" t="str">
+      <c r="I6" s="233"/>
+      <c r="J6" s="234" t="str">
         <f>D26</f>
         <v>Thermomètre</v>
       </c>
-      <c r="K6" s="229"/>
-      <c r="L6" s="229"/>
-      <c r="M6" s="228" t="s">
+      <c r="K6" s="234"/>
+      <c r="L6" s="234"/>
+      <c r="M6" s="233" t="s">
         <v>218</v>
       </c>
-      <c r="N6" s="228"/>
-      <c r="O6" s="228"/>
-      <c r="P6" s="223"/>
-      <c r="Q6" s="223"/>
-      <c r="R6" s="224"/>
+      <c r="N6" s="233"/>
+      <c r="O6" s="233"/>
+      <c r="P6" s="228"/>
+      <c r="Q6" s="228"/>
+      <c r="R6" s="229"/>
       <c r="S6" s="69"/>
     </row>
     <row r="7" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -4704,24 +4729,24 @@
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="70"/>
-      <c r="C8" s="189" t="s">
+      <c r="C8" s="193" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="190"/>
-      <c r="E8" s="190"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
-      <c r="H8" s="190"/>
-      <c r="I8" s="190"/>
-      <c r="J8" s="190"/>
-      <c r="K8" s="190"/>
-      <c r="L8" s="190"/>
-      <c r="M8" s="190"/>
-      <c r="N8" s="190"/>
-      <c r="O8" s="190"/>
-      <c r="P8" s="190"/>
-      <c r="Q8" s="190"/>
-      <c r="R8" s="191"/>
+      <c r="D8" s="194"/>
+      <c r="E8" s="194"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="194"/>
+      <c r="I8" s="194"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="194"/>
+      <c r="L8" s="194"/>
+      <c r="M8" s="194"/>
+      <c r="N8" s="194"/>
+      <c r="O8" s="194"/>
+      <c r="P8" s="194"/>
+      <c r="Q8" s="194"/>
+      <c r="R8" s="195"/>
       <c r="S8" s="71"/>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -4747,94 +4772,94 @@
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B10" s="79"/>
       <c r="C10" s="84"/>
-      <c r="D10" s="212" t="s">
+      <c r="D10" s="216" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="213"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="213"/>
-      <c r="H10" s="213"/>
-      <c r="I10" s="213"/>
-      <c r="J10" s="213"/>
-      <c r="K10" s="213"/>
-      <c r="L10" s="213"/>
-      <c r="M10" s="213"/>
-      <c r="N10" s="213"/>
-      <c r="O10" s="213"/>
-      <c r="P10" s="213"/>
-      <c r="Q10" s="214"/>
+      <c r="E10" s="217"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="217"/>
+      <c r="K10" s="217"/>
+      <c r="L10" s="217"/>
+      <c r="M10" s="217"/>
+      <c r="N10" s="217"/>
+      <c r="O10" s="217"/>
+      <c r="P10" s="217"/>
+      <c r="Q10" s="218"/>
       <c r="R10" s="85"/>
       <c r="S10" s="80"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B11" s="79"/>
       <c r="C11" s="84"/>
-      <c r="D11" s="230" t="s">
+      <c r="D11" s="235" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="231"/>
-      <c r="F11" s="232"/>
-      <c r="G11" s="233"/>
-      <c r="H11" s="234"/>
-      <c r="I11" s="234"/>
-      <c r="J11" s="235"/>
-      <c r="K11" s="230" t="s">
+      <c r="E11" s="236"/>
+      <c r="F11" s="237"/>
+      <c r="G11" s="238"/>
+      <c r="H11" s="239"/>
+      <c r="I11" s="239"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="235" t="s">
         <v>222</v>
       </c>
-      <c r="L11" s="231"/>
-      <c r="M11" s="232"/>
-      <c r="N11" s="236"/>
-      <c r="O11" s="237"/>
-      <c r="P11" s="237"/>
-      <c r="Q11" s="238"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="237"/>
+      <c r="N11" s="241"/>
+      <c r="O11" s="242"/>
+      <c r="P11" s="242"/>
+      <c r="Q11" s="243"/>
       <c r="R11" s="85"/>
       <c r="S11" s="80"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B12" s="79"/>
       <c r="C12" s="84"/>
-      <c r="D12" s="230" t="s">
+      <c r="D12" s="235" t="s">
         <v>220</v>
       </c>
-      <c r="E12" s="231"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="233"/>
-      <c r="H12" s="234"/>
-      <c r="I12" s="234"/>
-      <c r="J12" s="235"/>
-      <c r="K12" s="230" t="s">
+      <c r="E12" s="236"/>
+      <c r="F12" s="237"/>
+      <c r="G12" s="238"/>
+      <c r="H12" s="239"/>
+      <c r="I12" s="239"/>
+      <c r="J12" s="240"/>
+      <c r="K12" s="235" t="s">
         <v>223</v>
       </c>
-      <c r="L12" s="231"/>
-      <c r="M12" s="232"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="234"/>
-      <c r="P12" s="234"/>
-      <c r="Q12" s="235"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="237"/>
+      <c r="N12" s="238"/>
+      <c r="O12" s="239"/>
+      <c r="P12" s="239"/>
+      <c r="Q12" s="240"/>
       <c r="R12" s="85"/>
       <c r="S12" s="80"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B13" s="79"/>
       <c r="C13" s="84"/>
-      <c r="D13" s="230" t="s">
+      <c r="D13" s="235" t="s">
         <v>221</v>
       </c>
-      <c r="E13" s="231"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="233"/>
-      <c r="H13" s="234"/>
-      <c r="I13" s="234"/>
-      <c r="J13" s="235"/>
-      <c r="K13" s="230" t="s">
+      <c r="E13" s="236"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="239"/>
+      <c r="I13" s="239"/>
+      <c r="J13" s="240"/>
+      <c r="K13" s="235" t="s">
         <v>224</v>
       </c>
-      <c r="L13" s="231"/>
-      <c r="M13" s="232"/>
-      <c r="N13" s="239"/>
-      <c r="O13" s="240"/>
-      <c r="P13" s="240"/>
-      <c r="Q13" s="241"/>
+      <c r="L13" s="236"/>
+      <c r="M13" s="237"/>
+      <c r="N13" s="244"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="245"/>
+      <c r="Q13" s="246"/>
       <c r="R13" s="85"/>
       <c r="S13" s="80"/>
     </row>
@@ -4861,70 +4886,70 @@
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B15" s="79"/>
       <c r="C15" s="84"/>
-      <c r="D15" s="242" t="s">
+      <c r="D15" s="247" t="s">
         <v>192</v>
       </c>
-      <c r="E15" s="242"/>
-      <c r="F15" s="242"/>
-      <c r="G15" s="242"/>
-      <c r="H15" s="242"/>
-      <c r="I15" s="242"/>
-      <c r="J15" s="242"/>
-      <c r="K15" s="242"/>
-      <c r="L15" s="242"/>
-      <c r="M15" s="242"/>
-      <c r="N15" s="242"/>
-      <c r="O15" s="242"/>
-      <c r="P15" s="242"/>
-      <c r="Q15" s="242"/>
+      <c r="E15" s="247"/>
+      <c r="F15" s="247"/>
+      <c r="G15" s="247"/>
+      <c r="H15" s="247"/>
+      <c r="I15" s="247"/>
+      <c r="J15" s="247"/>
+      <c r="K15" s="247"/>
+      <c r="L15" s="247"/>
+      <c r="M15" s="247"/>
+      <c r="N15" s="247"/>
+      <c r="O15" s="247"/>
+      <c r="P15" s="247"/>
+      <c r="Q15" s="247"/>
       <c r="R15" s="85"/>
       <c r="S15" s="80"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B16" s="79"/>
       <c r="C16" s="84"/>
-      <c r="D16" s="230" t="s">
+      <c r="D16" s="235" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="231"/>
-      <c r="F16" s="232"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="234"/>
-      <c r="I16" s="234"/>
-      <c r="J16" s="235"/>
-      <c r="K16" s="230" t="s">
+      <c r="E16" s="236"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="238"/>
+      <c r="H16" s="239"/>
+      <c r="I16" s="239"/>
+      <c r="J16" s="240"/>
+      <c r="K16" s="235" t="s">
         <v>225</v>
       </c>
-      <c r="L16" s="231"/>
-      <c r="M16" s="232"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="234"/>
-      <c r="P16" s="234"/>
-      <c r="Q16" s="235"/>
+      <c r="L16" s="236"/>
+      <c r="M16" s="237"/>
+      <c r="N16" s="238"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="239"/>
+      <c r="Q16" s="240"/>
       <c r="R16" s="85"/>
       <c r="S16" s="80"/>
     </row>
     <row r="17" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B17" s="79"/>
       <c r="C17" s="84"/>
-      <c r="D17" s="230" t="s">
+      <c r="D17" s="235" t="s">
         <v>220</v>
       </c>
-      <c r="E17" s="231"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="234"/>
-      <c r="J17" s="235"/>
-      <c r="K17" s="230" t="s">
+      <c r="E17" s="236"/>
+      <c r="F17" s="237"/>
+      <c r="G17" s="238"/>
+      <c r="H17" s="239"/>
+      <c r="I17" s="239"/>
+      <c r="J17" s="240"/>
+      <c r="K17" s="235" t="s">
         <v>226</v>
       </c>
-      <c r="L17" s="231"/>
-      <c r="M17" s="232"/>
-      <c r="N17" s="243"/>
-      <c r="O17" s="244"/>
-      <c r="P17" s="244"/>
-      <c r="Q17" s="245"/>
+      <c r="L17" s="236"/>
+      <c r="M17" s="237"/>
+      <c r="N17" s="248"/>
+      <c r="O17" s="249"/>
+      <c r="P17" s="249"/>
+      <c r="Q17" s="250"/>
       <c r="R17" s="85"/>
       <c r="S17" s="80"/>
     </row>
@@ -4951,18 +4976,18 @@
     <row r="19" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B19" s="79"/>
       <c r="C19" s="84"/>
-      <c r="D19" s="212" t="s">
+      <c r="D19" s="216" t="s">
         <v>190</v>
       </c>
-      <c r="E19" s="213"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="213"/>
-      <c r="H19" s="213"/>
-      <c r="I19" s="213"/>
-      <c r="J19" s="213"/>
-      <c r="K19" s="213"/>
-      <c r="L19" s="213"/>
-      <c r="M19" s="214"/>
+      <c r="E19" s="217"/>
+      <c r="F19" s="217"/>
+      <c r="G19" s="217"/>
+      <c r="H19" s="217"/>
+      <c r="I19" s="217"/>
+      <c r="J19" s="217"/>
+      <c r="K19" s="217"/>
+      <c r="L19" s="217"/>
+      <c r="M19" s="218"/>
       <c r="N19" s="77"/>
       <c r="O19" s="77"/>
       <c r="P19" s="77"/>
@@ -4973,26 +4998,26 @@
     <row r="20" spans="2:26" s="76" customFormat="1" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B20" s="73"/>
       <c r="C20" s="86"/>
-      <c r="D20" s="209" t="s">
+      <c r="D20" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="209"/>
-      <c r="F20" s="210" t="s">
+      <c r="E20" s="213"/>
+      <c r="F20" s="214" t="s">
         <v>203</v>
       </c>
-      <c r="G20" s="209"/>
-      <c r="H20" s="210" t="s">
+      <c r="G20" s="213"/>
+      <c r="H20" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I20" s="210"/>
-      <c r="J20" s="210" t="s">
+      <c r="I20" s="214"/>
+      <c r="J20" s="214" t="s">
         <v>76</v>
       </c>
-      <c r="K20" s="210"/>
-      <c r="L20" s="211" t="s">
+      <c r="K20" s="214"/>
+      <c r="L20" s="215" t="s">
         <v>191</v>
       </c>
-      <c r="M20" s="211"/>
+      <c r="M20" s="215"/>
       <c r="N20" s="74"/>
       <c r="O20" s="74"/>
       <c r="P20" s="74"/>
@@ -5010,19 +5035,19 @@
     <row r="21" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B21" s="79"/>
       <c r="C21" s="84"/>
-      <c r="D21" s="199"/>
-      <c r="E21" s="200"/>
-      <c r="F21" s="199"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="199"/>
-      <c r="I21" s="200"/>
-      <c r="J21" s="199"/>
-      <c r="K21" s="200"/>
-      <c r="L21" s="201" t="str">
+      <c r="D21" s="203"/>
+      <c r="E21" s="204"/>
+      <c r="F21" s="203"/>
+      <c r="G21" s="204"/>
+      <c r="H21" s="203"/>
+      <c r="I21" s="204"/>
+      <c r="J21" s="203"/>
+      <c r="K21" s="204"/>
+      <c r="L21" s="205" t="str">
         <f>IF(H21&gt;0,H21-J21,"-")</f>
         <v>-</v>
       </c>
-      <c r="M21" s="202"/>
+      <c r="M21" s="206"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -5072,24 +5097,24 @@
     </row>
     <row r="24" spans="2:26" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B24" s="79"/>
-      <c r="C24" s="189" t="s">
+      <c r="C24" s="193" t="s">
         <v>205</v>
       </c>
-      <c r="D24" s="190"/>
-      <c r="E24" s="190"/>
-      <c r="F24" s="190"/>
-      <c r="G24" s="190"/>
-      <c r="H24" s="190"/>
-      <c r="I24" s="190"/>
-      <c r="J24" s="190"/>
-      <c r="K24" s="190"/>
-      <c r="L24" s="190"/>
-      <c r="M24" s="190"/>
-      <c r="N24" s="190"/>
-      <c r="O24" s="190"/>
-      <c r="P24" s="190"/>
-      <c r="Q24" s="190"/>
-      <c r="R24" s="191"/>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="194"/>
+      <c r="G24" s="194"/>
+      <c r="H24" s="194"/>
+      <c r="I24" s="194"/>
+      <c r="J24" s="194"/>
+      <c r="K24" s="194"/>
+      <c r="L24" s="194"/>
+      <c r="M24" s="194"/>
+      <c r="N24" s="194"/>
+      <c r="O24" s="194"/>
+      <c r="P24" s="194"/>
+      <c r="Q24" s="194"/>
+      <c r="R24" s="195"/>
       <c r="S24" s="80"/>
     </row>
     <row r="25" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5115,46 +5140,46 @@
     <row r="26" spans="2:26" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B26" s="79"/>
       <c r="C26" s="91"/>
-      <c r="D26" s="203" t="s">
+      <c r="D26" s="207" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="203"/>
-      <c r="F26" s="203"/>
-      <c r="G26" s="203"/>
-      <c r="H26" s="203"/>
-      <c r="I26" s="203"/>
-      <c r="J26" s="203"/>
-      <c r="K26" s="203"/>
-      <c r="L26" s="203"/>
-      <c r="M26" s="203"/>
-      <c r="N26" s="203"/>
-      <c r="O26" s="203"/>
-      <c r="P26" s="203"/>
-      <c r="Q26" s="203"/>
+      <c r="E26" s="207"/>
+      <c r="F26" s="207"/>
+      <c r="G26" s="207"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="207"/>
+      <c r="J26" s="207"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="207"/>
+      <c r="Q26" s="207"/>
       <c r="R26" s="92"/>
       <c r="S26" s="80"/>
     </row>
     <row r="27" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B27" s="79"/>
       <c r="C27" s="91"/>
-      <c r="D27" s="179" t="s">
+      <c r="D27" s="183" t="s">
         <v>188</v>
       </c>
-      <c r="E27" s="180"/>
-      <c r="F27" s="180"/>
-      <c r="G27" s="180"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="181"/>
-      <c r="J27" s="179" t="s">
+      <c r="E27" s="184"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="184"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="183" t="s">
         <v>176</v>
       </c>
-      <c r="K27" s="180"/>
-      <c r="L27" s="180"/>
-      <c r="M27" s="181"/>
-      <c r="N27" s="204" t="s">
+      <c r="K27" s="184"/>
+      <c r="L27" s="184"/>
+      <c r="M27" s="185"/>
+      <c r="N27" s="208" t="s">
         <v>77</v>
       </c>
-      <c r="O27" s="204"/>
+      <c r="O27" s="208"/>
       <c r="P27" s="98" t="s">
         <v>189</v>
       </c>
@@ -5173,23 +5198,23 @@
       <c r="D28" s="93">
         <v>1</v>
       </c>
-      <c r="E28" s="182" t="str">
+      <c r="E28" s="186" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D28+2,FALSE),"-")</f>
         <v>L'accès à l'ouvrage et aux équipements de mesure se fait-il en toute sécurité pour les agents en charge des opérations de contrôles et d'entretien ?</v>
       </c>
-      <c r="F28" s="183"/>
-      <c r="G28" s="183"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="183"/>
-      <c r="J28" s="182" t="str">
+      <c r="F28" s="187"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="187"/>
+      <c r="I28" s="187"/>
+      <c r="J28" s="186" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D28+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>En cas d'accès nécessitant des équipements de protection individuels renforcés (ARI par exemple) ou d'intervenir à 2 personnes, retenir "Validé avec réserve"</v>
       </c>
-      <c r="K28" s="183"/>
-      <c r="L28" s="183"/>
-      <c r="M28" s="184"/>
-      <c r="N28" s="187"/>
-      <c r="O28" s="188"/>
+      <c r="K28" s="187"/>
+      <c r="L28" s="187"/>
+      <c r="M28" s="188"/>
+      <c r="N28" s="191"/>
+      <c r="O28" s="192"/>
       <c r="P28" s="99">
         <f>IF(OR(N28="Validé",N28="Réserve",N28="Oui"),Q28,0)</f>
         <v>0</v>
@@ -5200,8 +5225,9 @@
       </c>
       <c r="R28" s="92"/>
       <c r="S28" s="80"/>
-      <c r="U28" s="176" t="s">
-        <v>39</v>
+      <c r="U28" s="176" t="str" cm="1">
+        <f t="array" ref="U28">IFERROR(INDEX(Critères!$B$3:$BZ$16, D28+2, MATCH($D$26, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="29" spans="2:26" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5210,23 +5236,23 @@
       <c r="D29" s="93">
         <v>2</v>
       </c>
-      <c r="E29" s="182" t="str">
+      <c r="E29" s="186" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D29+2,FALSE),"-")</f>
         <v>La sonde est-elle installée conformément aux règles de l'art et/ou aux prescriptions des constructeurs ?</v>
       </c>
-      <c r="F29" s="183"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="182" t="str">
+      <c r="F29" s="187"/>
+      <c r="G29" s="187"/>
+      <c r="H29" s="187"/>
+      <c r="I29" s="187"/>
+      <c r="J29" s="186" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D29+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>Dans le canal de rejet, au centre de l'écoulement, à 2/3 de la profondeur et façon à être toujours immergé et à l'ombre.</v>
       </c>
-      <c r="K29" s="183"/>
-      <c r="L29" s="183"/>
-      <c r="M29" s="184"/>
-      <c r="N29" s="187"/>
-      <c r="O29" s="188"/>
+      <c r="K29" s="187"/>
+      <c r="L29" s="187"/>
+      <c r="M29" s="188"/>
+      <c r="N29" s="191"/>
+      <c r="O29" s="192"/>
       <c r="P29" s="99">
         <f t="shared" ref="P29:P31" si="0">IF(OR(N29="Validé",N29="Réserve",N29="Oui"),Q29,0)</f>
         <v>0</v>
@@ -5237,8 +5263,9 @@
       </c>
       <c r="R29" s="92"/>
       <c r="S29" s="80"/>
-      <c r="U29" s="176" t="s">
-        <v>39</v>
+      <c r="U29" s="176" t="str" cm="1">
+        <f t="array" ref="U29">IFERROR(INDEX(Critères!$B$3:$BZ$16, D29+2, MATCH($D$26, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="30" spans="2:26" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5247,24 +5274,24 @@
       <c r="D30" s="93">
         <v>3</v>
       </c>
-      <c r="E30" s="182" t="str">
+      <c r="E30" s="186" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D30+2,FALSE),"-")</f>
         <v>La propreté et l'état d'entretien de la sonde, sont-ils satisfaisants ?</v>
       </c>
-      <c r="F30" s="183"/>
-      <c r="G30" s="183"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="183"/>
-      <c r="J30" s="182" t="str">
+      <c r="F30" s="187"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="186" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D30+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>Un défaut de propreté et/ou d'entretien ayant un impact immédiat sur la fiabilité de la mesure doit entrainer un jugement à "Non Validé".
 Un défaut de propreté et/ou d'entretien mais n'ayant à priori pas d'impact immédiat sur la fiabilité de la mesure doit avoir un jugement "Validé avec réserve".</v>
       </c>
-      <c r="K30" s="183"/>
-      <c r="L30" s="183"/>
-      <c r="M30" s="184"/>
-      <c r="N30" s="187"/>
-      <c r="O30" s="188"/>
+      <c r="K30" s="187"/>
+      <c r="L30" s="187"/>
+      <c r="M30" s="188"/>
+      <c r="N30" s="191"/>
+      <c r="O30" s="192"/>
       <c r="P30" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5275,8 +5302,9 @@
       </c>
       <c r="R30" s="92"/>
       <c r="S30" s="80"/>
-      <c r="U30" s="176" t="s">
-        <v>39</v>
+      <c r="U30" s="176" t="str" cm="1">
+        <f t="array" ref="U30">IFERROR(INDEX(Critères!$B$3:$BZ$16, D30+2, MATCH($D$26, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="31" spans="2:26" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5285,26 +5313,26 @@
       <c r="D31" s="93">
         <v>4</v>
       </c>
-      <c r="E31" s="182" t="str">
+      <c r="E31" s="186" t="str">
         <f>IFERROR(HLOOKUP($D$26,Critères!$B$3:$BY$16,D31+2,FALSE),"-")</f>
         <v>L'écart entre d'une part la mesure de la température réalisée à partir du dispositif en place et celle réalisée par l'organisme de contrôle d'autre part, est-il cohérent (EMT ± 1°C) ?</v>
       </c>
-      <c r="F31" s="183"/>
-      <c r="G31" s="183"/>
-      <c r="H31" s="183"/>
-      <c r="I31" s="183"/>
-      <c r="J31" s="182" t="str">
+      <c r="F31" s="187"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="186" t="str">
         <f>IFERROR(INDEX(Critères!$B$3:$BY$16, D31+2, MATCH($D$26, Critères!$B$3:$BY$3, 0) + 1),"-")</f>
         <v>-</v>
       </c>
-      <c r="K31" s="183"/>
-      <c r="L31" s="183"/>
-      <c r="M31" s="184"/>
-      <c r="N31" s="187" t="str">
+      <c r="K31" s="187"/>
+      <c r="L31" s="187"/>
+      <c r="M31" s="188"/>
+      <c r="N31" s="191" t="str">
         <f>IF(L21&lt;&gt;"-",IF(ABS(L21)&lt;=1,"Validé","Non validé"),"Non contrôlé")</f>
         <v>Non contrôlé</v>
       </c>
-      <c r="O31" s="188"/>
+      <c r="O31" s="192"/>
       <c r="P31" s="99">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5315,57 +5343,58 @@
       </c>
       <c r="R31" s="92"/>
       <c r="S31" s="80"/>
-      <c r="U31" s="176" t="s">
-        <v>39</v>
+      <c r="U31" s="176" t="str" cm="1">
+        <f t="array" ref="U31">IFERROR(INDEX(Critères!$B$3:$BZ$16, D31+2, MATCH($D$26, Critères!$B$3:$BZ$3, 0) + 3),"")</f>
+        <v>LISTE_3</v>
       </c>
     </row>
     <row r="32" spans="2:26" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B32" s="79"/>
       <c r="C32" s="91"/>
-      <c r="D32" s="185" t="s">
+      <c r="D32" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
-      <c r="N32" s="186"/>
-      <c r="O32" s="186"/>
-      <c r="P32" s="186" t="s">
+      <c r="E32" s="189"/>
+      <c r="F32" s="189"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="189"/>
+      <c r="L32" s="189"/>
+      <c r="M32" s="189"/>
+      <c r="N32" s="190"/>
+      <c r="O32" s="190"/>
+      <c r="P32" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="Q32" s="186"/>
+      <c r="Q32" s="190"/>
       <c r="R32" s="92"/>
       <c r="S32" s="80"/>
     </row>
     <row r="33" spans="2:19" ht="99.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B33" s="79"/>
       <c r="C33" s="91"/>
-      <c r="D33" s="205"/>
-      <c r="E33" s="205"/>
-      <c r="F33" s="205"/>
-      <c r="G33" s="205"/>
-      <c r="H33" s="205"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="205"/>
-      <c r="K33" s="205"/>
-      <c r="L33" s="205"/>
-      <c r="M33" s="205"/>
-      <c r="N33" s="206" t="str">
+      <c r="D33" s="209"/>
+      <c r="E33" s="209"/>
+      <c r="F33" s="209"/>
+      <c r="G33" s="209"/>
+      <c r="H33" s="209"/>
+      <c r="I33" s="209"/>
+      <c r="J33" s="209"/>
+      <c r="K33" s="209"/>
+      <c r="L33" s="209"/>
+      <c r="M33" s="209"/>
+      <c r="N33" s="210" t="str">
         <f>IF(P33&gt;80,"Validé",IF(P33&lt;70,"Non Validé", "Réserve"))</f>
         <v>Non Validé</v>
       </c>
-      <c r="O33" s="206"/>
-      <c r="P33" s="207">
+      <c r="O33" s="210"/>
+      <c r="P33" s="211">
         <f>IF(SUM(P28:P31)&gt;100,100,SUM(P28:P31))</f>
         <v>0</v>
       </c>
-      <c r="Q33" s="208"/>
+      <c r="Q33" s="212"/>
       <c r="R33" s="92"/>
       <c r="S33" s="80"/>
     </row>
@@ -5411,124 +5440,124 @@
     </row>
     <row r="36" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="79"/>
-      <c r="C36" s="189" t="s">
+      <c r="C36" s="193" t="s">
         <v>206</v>
       </c>
-      <c r="D36" s="190"/>
-      <c r="E36" s="190"/>
-      <c r="F36" s="190"/>
-      <c r="G36" s="190"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="190"/>
-      <c r="J36" s="190"/>
-      <c r="K36" s="190"/>
-      <c r="L36" s="190"/>
-      <c r="M36" s="190"/>
-      <c r="N36" s="190"/>
-      <c r="O36" s="190"/>
-      <c r="P36" s="190"/>
-      <c r="Q36" s="190"/>
-      <c r="R36" s="191"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="194"/>
+      <c r="G36" s="194"/>
+      <c r="H36" s="194"/>
+      <c r="I36" s="194"/>
+      <c r="J36" s="194"/>
+      <c r="K36" s="194"/>
+      <c r="L36" s="194"/>
+      <c r="M36" s="194"/>
+      <c r="N36" s="194"/>
+      <c r="O36" s="194"/>
+      <c r="P36" s="194"/>
+      <c r="Q36" s="194"/>
+      <c r="R36" s="195"/>
       <c r="S36" s="80"/>
     </row>
     <row r="37" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B37" s="79"/>
-      <c r="C37" s="192"/>
-      <c r="D37" s="193"/>
-      <c r="E37" s="193"/>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="193"/>
-      <c r="L37" s="193"/>
-      <c r="M37" s="193"/>
-      <c r="N37" s="193"/>
-      <c r="O37" s="193"/>
-      <c r="P37" s="193"/>
-      <c r="Q37" s="193"/>
-      <c r="R37" s="194"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="197"/>
+      <c r="E37" s="197"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="197"/>
+      <c r="L37" s="197"/>
+      <c r="M37" s="197"/>
+      <c r="N37" s="197"/>
+      <c r="O37" s="197"/>
+      <c r="P37" s="197"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="198"/>
       <c r="S37" s="80"/>
     </row>
     <row r="38" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="79"/>
-      <c r="C38" s="195"/>
-      <c r="D38" s="193"/>
-      <c r="E38" s="193"/>
-      <c r="F38" s="193"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="193"/>
-      <c r="K38" s="193"/>
-      <c r="L38" s="193"/>
-      <c r="M38" s="193"/>
-      <c r="N38" s="193"/>
-      <c r="O38" s="193"/>
-      <c r="P38" s="193"/>
-      <c r="Q38" s="193"/>
-      <c r="R38" s="194"/>
+      <c r="C38" s="199"/>
+      <c r="D38" s="197"/>
+      <c r="E38" s="197"/>
+      <c r="F38" s="197"/>
+      <c r="G38" s="197"/>
+      <c r="H38" s="197"/>
+      <c r="I38" s="197"/>
+      <c r="J38" s="197"/>
+      <c r="K38" s="197"/>
+      <c r="L38" s="197"/>
+      <c r="M38" s="197"/>
+      <c r="N38" s="197"/>
+      <c r="O38" s="197"/>
+      <c r="P38" s="197"/>
+      <c r="Q38" s="197"/>
+      <c r="R38" s="198"/>
       <c r="S38" s="80"/>
     </row>
     <row r="39" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="79"/>
-      <c r="C39" s="195"/>
-      <c r="D39" s="193"/>
-      <c r="E39" s="193"/>
-      <c r="F39" s="193"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
-      <c r="I39" s="193"/>
-      <c r="J39" s="193"/>
-      <c r="K39" s="193"/>
-      <c r="L39" s="193"/>
-      <c r="M39" s="193"/>
-      <c r="N39" s="193"/>
-      <c r="O39" s="193"/>
-      <c r="P39" s="193"/>
-      <c r="Q39" s="193"/>
-      <c r="R39" s="194"/>
+      <c r="C39" s="199"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="197"/>
+      <c r="J39" s="197"/>
+      <c r="K39" s="197"/>
+      <c r="L39" s="197"/>
+      <c r="M39" s="197"/>
+      <c r="N39" s="197"/>
+      <c r="O39" s="197"/>
+      <c r="P39" s="197"/>
+      <c r="Q39" s="197"/>
+      <c r="R39" s="198"/>
       <c r="S39" s="80"/>
     </row>
     <row r="40" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="79"/>
-      <c r="C40" s="195"/>
-      <c r="D40" s="193"/>
-      <c r="E40" s="193"/>
-      <c r="F40" s="193"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="193"/>
-      <c r="K40" s="193"/>
-      <c r="L40" s="193"/>
-      <c r="M40" s="193"/>
-      <c r="N40" s="193"/>
-      <c r="O40" s="193"/>
-      <c r="P40" s="193"/>
-      <c r="Q40" s="193"/>
-      <c r="R40" s="194"/>
+      <c r="C40" s="199"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="197"/>
+      <c r="J40" s="197"/>
+      <c r="K40" s="197"/>
+      <c r="L40" s="197"/>
+      <c r="M40" s="197"/>
+      <c r="N40" s="197"/>
+      <c r="O40" s="197"/>
+      <c r="P40" s="197"/>
+      <c r="Q40" s="197"/>
+      <c r="R40" s="198"/>
       <c r="S40" s="80"/>
     </row>
     <row r="41" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B41" s="79"/>
-      <c r="C41" s="196"/>
-      <c r="D41" s="197"/>
-      <c r="E41" s="197"/>
-      <c r="F41" s="197"/>
-      <c r="G41" s="197"/>
-      <c r="H41" s="197"/>
-      <c r="I41" s="197"/>
-      <c r="J41" s="197"/>
-      <c r="K41" s="197"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="197"/>
-      <c r="N41" s="197"/>
-      <c r="O41" s="197"/>
-      <c r="P41" s="197"/>
-      <c r="Q41" s="197"/>
-      <c r="R41" s="198"/>
+      <c r="C41" s="200"/>
+      <c r="D41" s="201"/>
+      <c r="E41" s="201"/>
+      <c r="F41" s="201"/>
+      <c r="G41" s="201"/>
+      <c r="H41" s="201"/>
+      <c r="I41" s="201"/>
+      <c r="J41" s="201"/>
+      <c r="K41" s="201"/>
+      <c r="L41" s="201"/>
+      <c r="M41" s="201"/>
+      <c r="N41" s="201"/>
+      <c r="O41" s="201"/>
+      <c r="P41" s="201"/>
+      <c r="Q41" s="201"/>
+      <c r="R41" s="202"/>
       <c r="S41" s="80"/>
     </row>
     <row r="42" spans="2:19" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5552,7 +5581,7 @@
       <c r="S42" s="83"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dwJ2ZG5RP+WgsIbnZse7/BsKh1CnMoIOzeADS1oIZHc2kw4e2AsUcQCY9kItX+iIev5OOAYiUyPoCZLQ4hljeg==" saltValue="nTbIqis5kT/d4y6YCOqxTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GSJ4Kf423yTxZwc2XeipxiJD8y8d2kO0XytzHUvq9tbA9dds0IbjcNTOuhrepem0EwogjuYM9gGgBDEX0d2wdA==" saltValue="xS8qwwy9DVidOS2DvCU//A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="84">
     <mergeCell ref="D15:Q15"/>
     <mergeCell ref="D16:F16"/>
@@ -16931,7 +16960,7 @@
       <c r="WE27" s="19"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NuOFOq/VHgCRz18NRZmm0y6s/ZSnveytFE+W9jC1blzo4YwEDkWO1ZnA4ZVKSUiYfZkgejj0a7SaxRa5B9q6Qg==" saltValue="l58riu/oPCDAyDRkLQ2DpQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4ioN2MCFpbXUYYr9IAeqJIGBuB29Fbo8Yjr+FN7Fkwa12QIyxB9Bt1kR/+XLWJYUzTao9Dt6kr2MQpIIShHMIg==" saltValue="2Hn8yx6k9IN7NiCt2O7k/A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16976,10 +17005,10 @@
       <c r="H3" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="246" t="s">
+      <c r="I3" s="251" t="s">
         <v>245</v>
       </c>
-      <c r="J3" s="247"/>
+      <c r="J3" s="252"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -17276,7 +17305,7 @@
       <c r="G20" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="H20" s="248" t="s">
+      <c r="H20" s="179" t="s">
         <v>307</v>
       </c>
       <c r="I20" s="116" t="s">
@@ -17445,7 +17474,7 @@
       <c r="C29" s="61" t="s">
         <v>291</v>
       </c>
-      <c r="D29" s="249" t="s">
+      <c r="D29" s="180" t="s">
         <v>310</v>
       </c>
       <c r="E29" s="61" t="s">
@@ -17468,7 +17497,7 @@
       <c r="C30" t="s">
         <v>292</v>
       </c>
-      <c r="D30" s="250" t="s">
+      <c r="D30" s="181" t="s">
         <v>312</v>
       </c>
       <c r="E30" s="8" t="s">
@@ -17491,7 +17520,7 @@
       <c r="C31" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="250" t="s">
+      <c r="D31" s="181" t="s">
         <v>314</v>
       </c>
       <c r="I31" s="113" t="s">
@@ -17511,7 +17540,7 @@
       <c r="C32" t="s">
         <v>294</v>
       </c>
-      <c r="D32" s="250" t="s">
+      <c r="D32" s="181" t="s">
         <v>315</v>
       </c>
       <c r="I32" s="113" t="s">
@@ -17621,7 +17650,7 @@
       <c r="F44" t="s">
         <v>173</v>
       </c>
-      <c r="G44" s="251" t="s">
+      <c r="G44" s="182" t="s">
         <v>316</v>
       </c>
     </row>
@@ -17644,7 +17673,7 @@
       <c r="F45" t="s">
         <v>174</v>
       </c>
-      <c r="G45" s="251" t="s">
+      <c r="G45" s="182" t="s">
         <v>82</v>
       </c>
     </row>
@@ -17667,7 +17696,7 @@
       <c r="F46" t="s">
         <v>172</v>
       </c>
-      <c r="G46" s="251" t="s">
+      <c r="G46" s="182" t="s">
         <v>178</v>
       </c>
     </row>
@@ -17681,7 +17710,7 @@
       <c r="E47" t="s">
         <v>109</v>
       </c>
-      <c r="G47" s="251" t="s">
+      <c r="G47" s="182" t="s">
         <v>317</v>
       </c>
     </row>
@@ -17748,7 +17777,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fhUqCP4nmdi7Ah7W+hh8CW3bHAFN48Bq7+w8qbJag7STQFRIWMrmhP1Ys2PMI16GsYd9Rar5xNrcWtI/K68kew==" saltValue="RNNMmb2vcLdOzQWgDKCpFw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FSH763fqpwtmVITixfT3fYIKxNSJcFY7rRR3RFhQwKaSLsQ+6es2FEfMRb84i3h1CESyAs9+Dq/eF0Ht+eIsIA==" saltValue="/1ELAohYs7xx588z1IW60Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H27">
     <sortCondition ref="H21:H27"/>
   </sortState>
@@ -17768,6 +17797,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:G5 E6:G12">
     <cfRule type="expression" priority="87">
+      <formula>IF($B$3="Industrie",1,0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H22">
+    <cfRule type="expression" priority="1">
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17791,32 +17825,12 @@
       <formula>IF($B$3="Industrie",1,0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H22">
-    <cfRule type="expression" priority="1">
-      <formula>IF($B$3="Industrie",1,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -18019,7 +18033,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
+    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -18036,29 +18084,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
-    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>